--- a/data/proteomics/protein_copy_statistical_top1000.xlsx
+++ b/data/proteomics/protein_copy_statistical_top1000.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY9"/>
+  <dimension ref="A1:BX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,152 +661,147 @@
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>D=0.027_M</t>
+          <t>mmol/gDW_Tyler_D0.1</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
+          <t>Min_ave_aerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Rich_ave_aerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Min_ave_anaerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Rich_ave_anaerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_REF_CN4_D=0.1</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_CN22_D=0.1</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_CN38_D=0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_CN75_D=0.1</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep1_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep2_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep3_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep4_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>molecular/cell_paxdb</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghaemmaghami et al. 2003 - Copy </t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Kulak et al. 2014 - Copy</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Copy number - Glucose</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Copy number - Galactose</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Copy number - Glycerol</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Mean molecules per cell_cell_system_2018</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Median molecules per cell_cell_system_2018</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
           <t>D=0.044_M</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>D=0.102_M</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>D=0.152_M</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>D=0.214_M</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>D=0.254_M</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>D=0.284_M</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>D=0.334_M</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>D=0.379_M</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>Min_ave_aerobic(mmol/gDW)</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>Rich_ave_aerobic(mmol/gDW)</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>Min_ave_anaerobic(mmol/gDW)</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>Rich_ave_anaerobic(mmol/gDW)</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_REF_CN4_D=0.1</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_CN22_D=0.1</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_CN38_D=0.1</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_CN75_D=0.1</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>FG_rep1_CN4_D= 0.26 or 0.32</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>FG_rep2_CN4_D= 0.26 or 0.32</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>FG_rep3_CN4_D= 0.26 or 0.32</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>FG_rep4_CN4_D= 0.26 or 0.32</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>molecular/cell_paxdb</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chong et al. 2015 - Copy </t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ghaemmaghami et al. 2003 - Copy </t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>Kulak et al. 2014 - Copy</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>Mean Copy number - Glucose</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>Mean Copy number - Galactose</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>Mean Copy number - Glycerol</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>Mean molecules per cell_cell_system_2018</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>Median molecules per cell_cell_system_2018</t>
         </is>
       </c>
     </row>
@@ -1041,9 +1036,6 @@
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
-      <c r="BY2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1052,16 +1044,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>182339.5903232239</v>
+        <v>118666.5729440651</v>
       </c>
       <c r="C3" t="n">
         <v>106756.1964861159</v>
       </c>
       <c r="D3" t="n">
-        <v>92809.76170128526</v>
+        <v>92809.76170128527</v>
       </c>
       <c r="E3" t="n">
-        <v>105064.9080032164</v>
+        <v>105064.9080032165</v>
       </c>
       <c r="F3" t="n">
         <v>38526.59640408488</v>
@@ -1076,10 +1068,10 @@
         <v>55166.83707125369</v>
       </c>
       <c r="J3" t="n">
-        <v>58873.38541922928</v>
+        <v>58873.38541922927</v>
       </c>
       <c r="K3" t="n">
-        <v>49578.10471780638</v>
+        <v>49578.1047178064</v>
       </c>
       <c r="L3" t="n">
         <v>28609.71781178535</v>
@@ -1112,19 +1104,19 @@
         <v>68188.02035978963</v>
       </c>
       <c r="V3" t="n">
-        <v>68302.5222594448</v>
+        <v>68302.52225944481</v>
       </c>
       <c r="W3" t="n">
         <v>64553.2746363598</v>
       </c>
       <c r="X3" t="n">
-        <v>84923.25512229698</v>
+        <v>84923.25512229696</v>
       </c>
       <c r="Y3" t="n">
         <v>89691.19445015978</v>
       </c>
       <c r="Z3" t="n">
-        <v>89384.77250020954</v>
+        <v>89384.77250020955</v>
       </c>
       <c r="AA3" t="n">
         <v>76682.69396234932</v>
@@ -1148,16 +1140,16 @@
         <v>30860.52910408555</v>
       </c>
       <c r="AH3" t="n">
-        <v>50473.06163056981</v>
+        <v>50473.06163056983</v>
       </c>
       <c r="AI3" t="n">
         <v>50109.96282314113</v>
       </c>
       <c r="AJ3" t="n">
-        <v>58125.27215142745</v>
+        <v>58125.27215142744</v>
       </c>
       <c r="AK3" t="n">
-        <v>72327.59058242064</v>
+        <v>72327.59058242066</v>
       </c>
       <c r="AL3" t="n">
         <v>62104.85691750223</v>
@@ -1166,22 +1158,22 @@
         <v>58413.23388771783</v>
       </c>
       <c r="AN3" t="n">
-        <v>52608.21437278811</v>
+        <v>52608.21437278812</v>
       </c>
       <c r="AO3" t="n">
-        <v>55482.51196158198</v>
+        <v>55482.51196158199</v>
       </c>
       <c r="AP3" t="n">
-        <v>46106.19990032678</v>
+        <v>46106.19990032677</v>
       </c>
       <c r="AQ3" t="n">
         <v>60214.95839389114</v>
       </c>
       <c r="AR3" t="n">
-        <v>51409.28057582908</v>
+        <v>51409.28057582907</v>
       </c>
       <c r="AS3" t="n">
-        <v>70178.35267045887</v>
+        <v>70178.35267045889</v>
       </c>
       <c r="AT3" t="n">
         <v>67282.09186947322</v>
@@ -1190,94 +1182,91 @@
         <v>65420.9956137284</v>
       </c>
       <c r="AV3" t="n">
-        <v>11633.72476849061</v>
+        <v>56218.47606892</v>
       </c>
       <c r="AW3" t="n">
-        <v>12593.11602799423</v>
+        <v>110958.0789014279</v>
       </c>
       <c r="AX3" t="n">
-        <v>13141.11911250513</v>
+        <v>114227.8779710944</v>
       </c>
       <c r="AY3" t="n">
-        <v>14614.09681533993</v>
+        <v>97932.30695506987</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14954.23111516985</v>
+        <v>101949.8285084604</v>
       </c>
       <c r="BA3" t="n">
-        <v>15107.53727441545</v>
+        <v>120801.1173720551</v>
       </c>
       <c r="BB3" t="n">
-        <v>15477.88421741095</v>
+        <v>76215.01799274819</v>
       </c>
       <c r="BC3" t="n">
-        <v>14402.35967420898</v>
+        <v>122161.0464563577</v>
       </c>
       <c r="BD3" t="n">
-        <v>14363.77408922464</v>
+        <v>62628.56142679702</v>
       </c>
       <c r="BE3" t="n">
-        <v>110958.0789014279</v>
+        <v>84972.93904289398</v>
       </c>
       <c r="BF3" t="n">
-        <v>114227.8779710944</v>
+        <v>83545.98291395989</v>
       </c>
       <c r="BG3" t="n">
-        <v>97932.30695506987</v>
+        <v>86777.87373623672</v>
       </c>
       <c r="BH3" t="n">
-        <v>101949.8285084604</v>
+        <v>84854.79851132452</v>
       </c>
       <c r="BI3" t="n">
-        <v>120801.1173720551</v>
+        <v>69468.56</v>
       </c>
       <c r="BJ3" t="n">
-        <v>76215.01799274819</v>
+        <v>41362.54604555698</v>
       </c>
       <c r="BK3" t="n">
-        <v>122161.0464563577</v>
+        <v>50762.72378200001</v>
       </c>
       <c r="BL3" t="n">
-        <v>62628.56142679701</v>
+        <v>60220.1</v>
       </c>
       <c r="BM3" t="n">
-        <v>84972.939042894</v>
+        <v>46466.519</v>
       </c>
       <c r="BN3" t="n">
-        <v>83545.98291395989</v>
+        <v>56764.487</v>
       </c>
       <c r="BO3" t="n">
-        <v>86777.87373623672</v>
+        <v>48056.15967633893</v>
       </c>
       <c r="BP3" t="n">
-        <v>84854.79851132451</v>
+        <v>30790.68569767767</v>
       </c>
       <c r="BQ3" t="n">
-        <v>69468.56</v>
+        <v>72950.20005716999</v>
       </c>
       <c r="BR3" t="n">
-        <v>1604.491721135234</v>
+        <v>79867.75266700535</v>
       </c>
       <c r="BS3" t="n">
-        <v>41362.54604555698</v>
+        <v>87516.54554463542</v>
       </c>
       <c r="BT3" t="n">
-        <v>50762.723782</v>
+        <v>64794.27683459198</v>
       </c>
       <c r="BU3" t="n">
-        <v>60220.1</v>
+        <v>75137.10070382195</v>
       </c>
       <c r="BV3" t="n">
-        <v>46466.519</v>
+        <v>77434.88225229445</v>
       </c>
       <c r="BW3" t="n">
-        <v>56764.487</v>
+        <v>80408.53506490916</v>
       </c>
       <c r="BX3" t="n">
-        <v>48056.15967633892</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>30790.68569767767</v>
+        <v>72536.49882266637</v>
       </c>
     </row>
     <row r="4">
@@ -1287,7 +1276,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2064890.70412621</v>
+        <v>473551.7256051206</v>
       </c>
       <c r="C4" t="n">
         <v>289125.1070240645</v>
@@ -1299,16 +1288,16 @@
         <v>265290.3972004985</v>
       </c>
       <c r="F4" t="n">
-        <v>114124.8546349758</v>
+        <v>114124.8546349757</v>
       </c>
       <c r="G4" t="n">
-        <v>103241.2458695453</v>
+        <v>103241.2458695452</v>
       </c>
       <c r="H4" t="n">
         <v>116074.2745859909</v>
       </c>
       <c r="I4" t="n">
-        <v>194741.9629844959</v>
+        <v>194741.9629844958</v>
       </c>
       <c r="J4" t="n">
         <v>213849.7020006684</v>
@@ -1320,7 +1309,7 @@
         <v>88033.84215074276</v>
       </c>
       <c r="M4" t="n">
-        <v>91808.13693407048</v>
+        <v>91808.1369340705</v>
       </c>
       <c r="N4" t="n">
         <v>116068.9523166056</v>
@@ -1365,7 +1354,7 @@
         <v>304067.2123832731</v>
       </c>
       <c r="AB4" t="n">
-        <v>358420.0042492593</v>
+        <v>358420.0042492592</v>
       </c>
       <c r="AC4" t="n">
         <v>358873.2615219346</v>
@@ -1377,7 +1366,7 @@
         <v>128192.2549721612</v>
       </c>
       <c r="AF4" t="n">
-        <v>164266.3687433068</v>
+        <v>164266.3687433067</v>
       </c>
       <c r="AG4" t="n">
         <v>84467.52871055336</v>
@@ -1413,7 +1402,7 @@
         <v>193950.9127080156</v>
       </c>
       <c r="AR4" t="n">
-        <v>154324.4473354668</v>
+        <v>154324.4473354669</v>
       </c>
       <c r="AS4" t="n">
         <v>202006.3943943077</v>
@@ -1425,94 +1414,91 @@
         <v>192631.4129956177</v>
       </c>
       <c r="AV4" t="n">
-        <v>28823.98021439242</v>
+        <v>116774.1687569073</v>
       </c>
       <c r="AW4" t="n">
-        <v>28873.43947038675</v>
+        <v>323028.6516446971</v>
       </c>
       <c r="AX4" t="n">
-        <v>23433.10885562455</v>
+        <v>341876.5071832517</v>
       </c>
       <c r="AY4" t="n">
-        <v>24150.84746603267</v>
+        <v>340809.411378612</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23842.27848378475</v>
+        <v>353206.8537280076</v>
       </c>
       <c r="BA4" t="n">
-        <v>24554.99687365268</v>
+        <v>302463.3125554243</v>
       </c>
       <c r="BB4" t="n">
-        <v>24543.33678280971</v>
+        <v>179555.3409466877</v>
       </c>
       <c r="BC4" t="n">
-        <v>23589.34672118556</v>
+        <v>297502.1754728873</v>
       </c>
       <c r="BD4" t="n">
-        <v>24059.92320292111</v>
+        <v>147978.1554881051</v>
       </c>
       <c r="BE4" t="n">
-        <v>323028.6516446971</v>
+        <v>198920.2825271324</v>
       </c>
       <c r="BF4" t="n">
-        <v>341876.5071832517</v>
+        <v>194530.08111154</v>
       </c>
       <c r="BG4" t="n">
-        <v>340809.411378612</v>
+        <v>201584.3046314215</v>
       </c>
       <c r="BH4" t="n">
-        <v>353206.8537280076</v>
+        <v>196143.1933133978</v>
       </c>
       <c r="BI4" t="n">
-        <v>302463.3125554243</v>
+        <v>130266.9026416543</v>
       </c>
       <c r="BJ4" t="n">
-        <v>179555.3409466878</v>
+        <v>104347.9899609492</v>
       </c>
       <c r="BK4" t="n">
-        <v>297502.1754728873</v>
+        <v>98800.7481366549</v>
       </c>
       <c r="BL4" t="n">
-        <v>147978.1554881051</v>
+        <v>132525.3106954099</v>
       </c>
       <c r="BM4" t="n">
-        <v>198920.2825271324</v>
+        <v>89022.93597954437</v>
       </c>
       <c r="BN4" t="n">
-        <v>194530.08111154</v>
+        <v>115875.8940212374</v>
       </c>
       <c r="BO4" t="n">
-        <v>201584.3046314215</v>
+        <v>105254.0294787811</v>
       </c>
       <c r="BP4" t="n">
-        <v>196143.1933133978</v>
+        <v>58464.14349249625</v>
       </c>
       <c r="BQ4" t="n">
-        <v>130266.9026416543</v>
+        <v>176927.7799525312</v>
       </c>
       <c r="BR4" t="n">
-        <v>2731.1832907684</v>
+        <v>149536.3129686544</v>
       </c>
       <c r="BS4" t="n">
-        <v>104347.9899609492</v>
+        <v>148794.6844269141</v>
       </c>
       <c r="BT4" t="n">
-        <v>98800.74813665492</v>
+        <v>104494.6003619383</v>
       </c>
       <c r="BU4" t="n">
-        <v>132525.3106954099</v>
+        <v>122672.8504187998</v>
       </c>
       <c r="BV4" t="n">
-        <v>89022.93597954439</v>
+        <v>124397.3728050634</v>
       </c>
       <c r="BW4" t="n">
-        <v>115875.8940212374</v>
+        <v>131096.9176983922</v>
       </c>
       <c r="BX4" t="n">
-        <v>105254.0294787811</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>58464.14349249625</v>
+        <v>120663.2753959248</v>
       </c>
     </row>
     <row r="5">
@@ -1522,7 +1508,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3113.81163847379</v>
+        <v>3107.197480626479</v>
       </c>
       <c r="C5" t="n">
         <v>3907.107878840001</v>
@@ -1660,94 +1646,91 @@
         <v>2066.88187568082</v>
       </c>
       <c r="AV5" t="n">
-        <v>1431.1513110972</v>
+        <v>4165.453600000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>1510.0556508092</v>
+        <v>4252.297358456579</v>
       </c>
       <c r="AX5" t="n">
-        <v>1850.1004431866</v>
+        <v>4702.352021166066</v>
       </c>
       <c r="AY5" t="n">
-        <v>2023.21550154108</v>
+        <v>4035.330859904059</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2061.34572006726</v>
+        <v>4348.50614279469</v>
       </c>
       <c r="BA5" t="n">
-        <v>2085.96831136166</v>
+        <v>8630.381030457032</v>
       </c>
       <c r="BB5" t="n">
-        <v>2075.20344427836</v>
+        <v>5798.559819150278</v>
       </c>
       <c r="BC5" t="n">
-        <v>1814.8095105833</v>
+        <v>9185.706454255054</v>
       </c>
       <c r="BD5" t="n">
-        <v>1790.73371806978</v>
+        <v>4808.572736454925</v>
       </c>
       <c r="BE5" t="n">
-        <v>4252.297358456579</v>
+        <v>5876.131610122532</v>
       </c>
       <c r="BF5" t="n">
-        <v>4702.352021166066</v>
+        <v>5650.116368655028</v>
       </c>
       <c r="BG5" t="n">
-        <v>4035.330859904059</v>
+        <v>6187.381591652433</v>
       </c>
       <c r="BH5" t="n">
-        <v>4348.50614279469</v>
+        <v>5992.074201495198</v>
       </c>
       <c r="BI5" t="n">
-        <v>8630.381030457032</v>
+        <v>10880</v>
       </c>
       <c r="BJ5" t="n">
-        <v>5798.559819150278</v>
+        <v>6024.12188755227</v>
       </c>
       <c r="BK5" t="n">
-        <v>9185.706454255054</v>
+        <v>4998.245</v>
       </c>
       <c r="BL5" t="n">
-        <v>4808.572736454925</v>
+        <v>4802</v>
       </c>
       <c r="BM5" t="n">
-        <v>5876.131610122532</v>
+        <v>4045</v>
       </c>
       <c r="BN5" t="n">
-        <v>5650.116368655028</v>
+        <v>5112</v>
       </c>
       <c r="BO5" t="n">
-        <v>6187.381591652433</v>
+        <v>9290.70616454881</v>
       </c>
       <c r="BP5" t="n">
-        <v>5992.074201495198</v>
+        <v>7300.91952348227</v>
       </c>
       <c r="BQ5" t="n">
-        <v>10880</v>
+        <v>7295.643844303476</v>
       </c>
       <c r="BR5" t="n">
-        <v>268.3123909773132</v>
+        <v>8870.156847249267</v>
       </c>
       <c r="BS5" t="n">
-        <v>6024.12188755227</v>
+        <v>9727.164099679872</v>
       </c>
       <c r="BT5" t="n">
-        <v>4998.245</v>
+        <v>7407.232072230986</v>
       </c>
       <c r="BU5" t="n">
-        <v>4802</v>
+        <v>8059.196314854126</v>
       </c>
       <c r="BV5" t="n">
-        <v>4045</v>
+        <v>8058.01094541416</v>
       </c>
       <c r="BW5" t="n">
-        <v>5112</v>
+        <v>8031.876061071963</v>
       </c>
       <c r="BX5" t="n">
-        <v>9290.70616454881</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>7300.91952348227</v>
+        <v>7106.518614424131</v>
       </c>
     </row>
     <row r="6">
@@ -1757,7 +1740,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6029.806541909054</v>
+        <v>6025.95949168564</v>
       </c>
       <c r="C6" t="n">
         <v>7216.527869111726</v>
@@ -1895,94 +1878,91 @@
         <v>4232.98804714863</v>
       </c>
       <c r="AV6" t="n">
-        <v>2521.535331302845</v>
+        <v>10983.90443333333</v>
       </c>
       <c r="AW6" t="n">
-        <v>2724.05184241993</v>
+        <v>7515.815423920358</v>
       </c>
       <c r="AX6" t="n">
-        <v>3071.820184998565</v>
+        <v>8120.698926603831</v>
       </c>
       <c r="AY6" t="n">
-        <v>3401.799415569005</v>
+        <v>7250.541152611133</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3508.61503267781</v>
+        <v>7650.553751903668</v>
       </c>
       <c r="BA6" t="n">
-        <v>3495.739436102045</v>
+        <v>16494.61059862406</v>
       </c>
       <c r="BB6" t="n">
-        <v>3472.20492412211</v>
+        <v>10875.52250551388</v>
       </c>
       <c r="BC6" t="n">
-        <v>3079.11772713501</v>
+        <v>17509.36708087136</v>
       </c>
       <c r="BD6" t="n">
-        <v>3078.185291716865</v>
+        <v>9064.389944347275</v>
       </c>
       <c r="BE6" t="n">
-        <v>7515.815423920358</v>
+        <v>10315.87191092336</v>
       </c>
       <c r="BF6" t="n">
-        <v>8120.698926603831</v>
+        <v>10179.24926280669</v>
       </c>
       <c r="BG6" t="n">
-        <v>7250.541152611133</v>
+        <v>10962.99629254136</v>
       </c>
       <c r="BH6" t="n">
-        <v>7650.553751903668</v>
+        <v>10720.83894146489</v>
       </c>
       <c r="BI6" t="n">
-        <v>16494.61059862406</v>
+        <v>16480</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10875.52250551388</v>
+        <v>7864.32899943488</v>
       </c>
       <c r="BK6" t="n">
-        <v>17509.36708087136</v>
+        <v>8484.61925</v>
       </c>
       <c r="BL6" t="n">
-        <v>9064.389944347275</v>
+        <v>8615.75</v>
       </c>
       <c r="BM6" t="n">
-        <v>10315.87191092336</v>
+        <v>7150.75</v>
       </c>
       <c r="BN6" t="n">
-        <v>10179.24926280669</v>
+        <v>9553.75</v>
       </c>
       <c r="BO6" t="n">
-        <v>10962.99629254136</v>
+        <v>13023.41370792537</v>
       </c>
       <c r="BP6" t="n">
-        <v>10720.83894146489</v>
+        <v>9911.003395444626</v>
       </c>
       <c r="BQ6" t="n">
-        <v>16480</v>
+        <v>13249.19716256196</v>
       </c>
       <c r="BR6" t="n">
-        <v>387.8296532957035</v>
+        <v>15739.09937999126</v>
       </c>
       <c r="BS6" t="n">
-        <v>7864.32899943488</v>
+        <v>17157.53058715043</v>
       </c>
       <c r="BT6" t="n">
-        <v>8484.61925</v>
+        <v>12671.56603839952</v>
       </c>
       <c r="BU6" t="n">
-        <v>8615.75</v>
+        <v>13669.8226236754</v>
       </c>
       <c r="BV6" t="n">
-        <v>7150.75</v>
+        <v>13586.43830529653</v>
       </c>
       <c r="BW6" t="n">
-        <v>9553.75</v>
+        <v>13635.31195705756</v>
       </c>
       <c r="BX6" t="n">
-        <v>13023.41370792537</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>9911.003395444626</v>
+        <v>12215.30587910782</v>
       </c>
     </row>
     <row r="7">
@@ -1992,7 +1972,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13498.78198685062</v>
+        <v>13389.96439458389</v>
       </c>
       <c r="C7" t="n">
         <v>16442.70140861564</v>
@@ -2130,94 +2110,91 @@
         <v>9575.0604508053</v>
       </c>
       <c r="AV7" t="n">
-        <v>4831.42115624894</v>
+        <v>26190.681</v>
       </c>
       <c r="AW7" t="n">
-        <v>5258.427313832221</v>
+        <v>15609.95655560721</v>
       </c>
       <c r="AX7" t="n">
-        <v>5703.44740184131</v>
+        <v>16276.91132421246</v>
       </c>
       <c r="AY7" t="n">
-        <v>6108.4256577564</v>
+        <v>16208.70304617097</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6324.609861685391</v>
+        <v>16242.13310949606</v>
       </c>
       <c r="BA7" t="n">
-        <v>6042.10052086883</v>
+        <v>33956.95077590895</v>
       </c>
       <c r="BB7" t="n">
-        <v>6198.56495595645</v>
+        <v>21910.83972995547</v>
       </c>
       <c r="BC7" t="n">
-        <v>5392.11099632205</v>
+        <v>36528.54552456376</v>
       </c>
       <c r="BD7" t="n">
-        <v>5430.61220408289</v>
+        <v>18743.13274653286</v>
       </c>
       <c r="BE7" t="n">
-        <v>15609.95655560721</v>
+        <v>20895.1139454473</v>
       </c>
       <c r="BF7" t="n">
-        <v>16276.91132421246</v>
+        <v>20645.72522610265</v>
       </c>
       <c r="BG7" t="n">
-        <v>16208.70304617097</v>
+        <v>22114.81404777861</v>
       </c>
       <c r="BH7" t="n">
-        <v>16242.13310949606</v>
+        <v>21761.65913837581</v>
       </c>
       <c r="BI7" t="n">
-        <v>33956.95077590895</v>
+        <v>28840</v>
       </c>
       <c r="BJ7" t="n">
-        <v>21910.83972995547</v>
+        <v>13112.9007092155</v>
       </c>
       <c r="BK7" t="n">
-        <v>36528.54552456376</v>
+        <v>17275.445</v>
       </c>
       <c r="BL7" t="n">
-        <v>18743.13274653286</v>
+        <v>16104.5</v>
       </c>
       <c r="BM7" t="n">
-        <v>20895.1139454473</v>
+        <v>14002</v>
       </c>
       <c r="BN7" t="n">
-        <v>20645.72522610265</v>
+        <v>17878</v>
       </c>
       <c r="BO7" t="n">
-        <v>22114.81404777861</v>
+        <v>20879.48415664675</v>
       </c>
       <c r="BP7" t="n">
-        <v>21761.65913837581</v>
+        <v>15366.954286114</v>
       </c>
       <c r="BQ7" t="n">
-        <v>28840</v>
+        <v>26714.12558138224</v>
       </c>
       <c r="BR7" t="n">
-        <v>639.6564962389432</v>
+        <v>30963.38759736533</v>
       </c>
       <c r="BS7" t="n">
-        <v>13112.9007092155</v>
+        <v>32869.87611887697</v>
       </c>
       <c r="BT7" t="n">
-        <v>17275.445</v>
+        <v>24488.04282112215</v>
       </c>
       <c r="BU7" t="n">
-        <v>16104.5</v>
+        <v>26808.61193964766</v>
       </c>
       <c r="BV7" t="n">
-        <v>14002</v>
+        <v>27600.8202719678</v>
       </c>
       <c r="BW7" t="n">
-        <v>17878</v>
+        <v>27110.01043305021</v>
       </c>
       <c r="BX7" t="n">
-        <v>20879.48415664675</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>15366.954286114</v>
+        <v>24344.8954868173</v>
       </c>
     </row>
     <row r="8">
@@ -2227,7 +2204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44147.30965111453</v>
+        <v>44031.08146310746</v>
       </c>
       <c r="C8" t="n">
         <v>55126.11925017054</v>
@@ -2365,94 +2342,91 @@
         <v>34872.7198678155</v>
       </c>
       <c r="AV8" t="n">
-        <v>10790.7828521922</v>
+        <v>58938.8195</v>
       </c>
       <c r="AW8" t="n">
-        <v>11867.9208667756</v>
+        <v>47926.83632931147</v>
       </c>
       <c r="AX8" t="n">
-        <v>12737.4438027716</v>
+        <v>49879.80816358644</v>
       </c>
       <c r="AY8" t="n">
-        <v>14179.74119629705</v>
+        <v>47102.71896187135</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14522.5548310612</v>
+        <v>43830.33723661795</v>
       </c>
       <c r="BA8" t="n">
-        <v>14474.9319830324</v>
+        <v>97900.59145410832</v>
       </c>
       <c r="BB8" t="n">
-        <v>14571.0157652224</v>
+        <v>62239.53125919632</v>
       </c>
       <c r="BC8" t="n">
-        <v>13429.23932805895</v>
+        <v>99410.86126558285</v>
       </c>
       <c r="BD8" t="n">
-        <v>13318.2783836553</v>
+        <v>51836.51446690784</v>
       </c>
       <c r="BE8" t="n">
-        <v>47926.83632931147</v>
+        <v>59163.12972596447</v>
       </c>
       <c r="BF8" t="n">
-        <v>49879.80816358644</v>
+        <v>57568.7952600243</v>
       </c>
       <c r="BG8" t="n">
-        <v>47102.71896187135</v>
+        <v>62052.53102559906</v>
       </c>
       <c r="BH8" t="n">
-        <v>43830.33723661795</v>
+        <v>61265.22755491319</v>
       </c>
       <c r="BI8" t="n">
-        <v>97900.59145410832</v>
+        <v>66740</v>
       </c>
       <c r="BJ8" t="n">
-        <v>62239.53125919632</v>
+        <v>33667.77899637665</v>
       </c>
       <c r="BK8" t="n">
-        <v>99410.86126558285</v>
+        <v>44654.505</v>
       </c>
       <c r="BL8" t="n">
-        <v>51836.51446690784</v>
+        <v>42865</v>
       </c>
       <c r="BM8" t="n">
-        <v>59163.12972596447</v>
+        <v>37320.75</v>
       </c>
       <c r="BN8" t="n">
-        <v>57568.7952600243</v>
+        <v>48212</v>
       </c>
       <c r="BO8" t="n">
-        <v>62052.53102559906</v>
+        <v>49682.72769359915</v>
       </c>
       <c r="BP8" t="n">
-        <v>61265.22755491319</v>
+        <v>31746.90135544375</v>
       </c>
       <c r="BQ8" t="n">
-        <v>66740</v>
+        <v>66704.75722169633</v>
       </c>
       <c r="BR8" t="n">
-        <v>1610.427274230734</v>
+        <v>79159.61374579441</v>
       </c>
       <c r="BS8" t="n">
-        <v>33667.77899637665</v>
+        <v>85452.05509517266</v>
       </c>
       <c r="BT8" t="n">
-        <v>44654.505</v>
+        <v>64971.29226966516</v>
       </c>
       <c r="BU8" t="n">
-        <v>42865</v>
+        <v>76318.50865996671</v>
       </c>
       <c r="BV8" t="n">
-        <v>37320.75</v>
+        <v>79502.08765670167</v>
       </c>
       <c r="BW8" t="n">
-        <v>48212</v>
+        <v>77635.48292601698</v>
       </c>
       <c r="BX8" t="n">
-        <v>49682.72769359915</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>31746.90135544375</v>
+        <v>67920.31197821039</v>
       </c>
     </row>
     <row r="9">
@@ -2462,7 +2436,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63676124.5766395</v>
+        <v>8122726.592434363</v>
       </c>
       <c r="C9" t="n">
         <v>3086139.294757853</v>
@@ -2600,94 +2574,91 @@
         <v>2736623.22405714</v>
       </c>
       <c r="AV9" t="n">
-        <v>638547.362616218</v>
+        <v>2040565.936933333</v>
       </c>
       <c r="AW9" t="n">
-        <v>599863.015441888</v>
+        <v>2650588.786217585</v>
       </c>
       <c r="AX9" t="n">
-        <v>353129.611035564</v>
+        <v>2980879.128088631</v>
       </c>
       <c r="AY9" t="n">
-        <v>269478.800759234</v>
+        <v>5498558.33502333</v>
       </c>
       <c r="AZ9" t="n">
-        <v>275951.60535866</v>
+        <v>5568349.405127079</v>
       </c>
       <c r="BA9" t="n">
-        <v>275969.221390786</v>
+        <v>3672230.851263796</v>
       </c>
       <c r="BB9" t="n">
-        <v>281559.928552012</v>
+        <v>2530817.22048714</v>
       </c>
       <c r="BC9" t="n">
-        <v>262067.462541082</v>
+        <v>3841111.080042755</v>
       </c>
       <c r="BD9" t="n">
-        <v>264153.73905921</v>
+        <v>2055972.214523255</v>
       </c>
       <c r="BE9" t="n">
-        <v>2650588.786217585</v>
+        <v>2325577.519082672</v>
       </c>
       <c r="BF9" t="n">
-        <v>2980879.128088631</v>
+        <v>2181179.000166196</v>
       </c>
       <c r="BG9" t="n">
-        <v>5498558.33502333</v>
+        <v>2348400.968177486</v>
       </c>
       <c r="BH9" t="n">
-        <v>5568349.405127079</v>
+        <v>2267621.734259108</v>
       </c>
       <c r="BI9" t="n">
-        <v>3672230.851263796</v>
+        <v>1643440</v>
       </c>
       <c r="BJ9" t="n">
-        <v>2530817.22048714</v>
+        <v>1589836.91145789</v>
       </c>
       <c r="BK9" t="n">
-        <v>3841111.080042755</v>
+        <v>1575311</v>
       </c>
       <c r="BL9" t="n">
-        <v>2055972.214523255</v>
+        <v>1276423</v>
       </c>
       <c r="BM9" t="n">
-        <v>2325577.519082672</v>
+        <v>816687</v>
       </c>
       <c r="BN9" t="n">
-        <v>2181179.000166196</v>
+        <v>1270793</v>
       </c>
       <c r="BO9" t="n">
-        <v>2348400.968177486</v>
+        <v>1392598.80028636</v>
       </c>
       <c r="BP9" t="n">
-        <v>2267621.734259108</v>
+        <v>746357.568074079</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1643440</v>
+        <v>3563066.28214841</v>
       </c>
       <c r="BR9" t="n">
-        <v>24728.0311202142</v>
+        <v>2186908.808510384</v>
       </c>
       <c r="BS9" t="n">
-        <v>1589836.91145789</v>
+        <v>1526611.414481163</v>
       </c>
       <c r="BT9" t="n">
-        <v>1575311</v>
+        <v>1197000.573967651</v>
       </c>
       <c r="BU9" t="n">
-        <v>1276423</v>
+        <v>1459414.066163923</v>
       </c>
       <c r="BV9" t="n">
-        <v>816687</v>
+        <v>1515763.911566187</v>
       </c>
       <c r="BW9" t="n">
-        <v>1270793</v>
+        <v>1527797.363900427</v>
       </c>
       <c r="BX9" t="n">
-        <v>1392598.80028636</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>746357.568074079</v>
+        <v>1382972.910274663</v>
       </c>
     </row>
   </sheetData>

--- a/data/proteomics/protein_copy_statistical_top1000.xlsx
+++ b/data/proteomics/protein_copy_statistical_top1000.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX9"/>
+  <dimension ref="A1:BY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,40 +766,45 @@
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
+          <t>D=0.027_M</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
           <t>D=0.044_M</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>D=0.102_M</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>D=0.152_M</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>D=0.214_M</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>D=0.254_M</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>D=0.284_M</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>D=0.334_M</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>D=0.379_M</t>
         </is>
@@ -1036,6 +1041,9 @@
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
+      <c r="BY2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1053,7 +1061,7 @@
         <v>92809.76170128527</v>
       </c>
       <c r="E3" t="n">
-        <v>105064.9080032165</v>
+        <v>105064.9080032164</v>
       </c>
       <c r="F3" t="n">
         <v>38526.59640408488</v>
@@ -1068,10 +1076,10 @@
         <v>55166.83707125369</v>
       </c>
       <c r="J3" t="n">
-        <v>58873.38541922927</v>
+        <v>58873.38541922928</v>
       </c>
       <c r="K3" t="n">
-        <v>49578.1047178064</v>
+        <v>49578.10471780638</v>
       </c>
       <c r="L3" t="n">
         <v>28609.71781178535</v>
@@ -1113,13 +1121,13 @@
         <v>84923.25512229696</v>
       </c>
       <c r="Y3" t="n">
-        <v>89691.19445015978</v>
+        <v>89691.19445015976</v>
       </c>
       <c r="Z3" t="n">
-        <v>89384.77250020955</v>
+        <v>89384.77250020954</v>
       </c>
       <c r="AA3" t="n">
-        <v>76682.69396234932</v>
+        <v>76682.69396234934</v>
       </c>
       <c r="AB3" t="n">
         <v>92758.04731701875</v>
@@ -1134,7 +1142,7 @@
         <v>43122.94808525473</v>
       </c>
       <c r="AF3" t="n">
-        <v>53698.23620652137</v>
+        <v>53698.23620652136</v>
       </c>
       <c r="AG3" t="n">
         <v>30860.52910408555</v>
@@ -1158,10 +1166,10 @@
         <v>58413.23388771783</v>
       </c>
       <c r="AN3" t="n">
-        <v>52608.21437278812</v>
+        <v>52608.21437278811</v>
       </c>
       <c r="AO3" t="n">
-        <v>55482.51196158199</v>
+        <v>55482.51196158198</v>
       </c>
       <c r="AP3" t="n">
         <v>46106.19990032677</v>
@@ -1185,19 +1193,19 @@
         <v>56218.47606892</v>
       </c>
       <c r="AW3" t="n">
-        <v>110958.0789014279</v>
+        <v>110958.078901428</v>
       </c>
       <c r="AX3" t="n">
         <v>114227.8779710944</v>
       </c>
       <c r="AY3" t="n">
-        <v>97932.30695506987</v>
+        <v>97932.30695506986</v>
       </c>
       <c r="AZ3" t="n">
         <v>101949.8285084604</v>
       </c>
       <c r="BA3" t="n">
-        <v>120801.1173720551</v>
+        <v>120801.117372055</v>
       </c>
       <c r="BB3" t="n">
         <v>76215.01799274819</v>
@@ -1209,7 +1217,7 @@
         <v>62628.56142679702</v>
       </c>
       <c r="BE3" t="n">
-        <v>84972.93904289398</v>
+        <v>84972.93904289401</v>
       </c>
       <c r="BF3" t="n">
         <v>83545.98291395989</v>
@@ -1218,7 +1226,7 @@
         <v>86777.87373623672</v>
       </c>
       <c r="BH3" t="n">
-        <v>84854.79851132452</v>
+        <v>84854.79851132451</v>
       </c>
       <c r="BI3" t="n">
         <v>69468.56</v>
@@ -1227,7 +1235,7 @@
         <v>41362.54604555698</v>
       </c>
       <c r="BK3" t="n">
-        <v>50762.72378200001</v>
+        <v>50762.72378199999</v>
       </c>
       <c r="BL3" t="n">
         <v>60220.1</v>
@@ -1245,28 +1253,31 @@
         <v>30790.68569767767</v>
       </c>
       <c r="BQ3" t="n">
+        <v>70924.98469309551</v>
+      </c>
+      <c r="BR3" t="n">
         <v>72950.20005716999</v>
       </c>
-      <c r="BR3" t="n">
-        <v>79867.75266700535</v>
-      </c>
       <c r="BS3" t="n">
+        <v>79867.75266700536</v>
+      </c>
+      <c r="BT3" t="n">
         <v>87516.54554463542</v>
       </c>
-      <c r="BT3" t="n">
+      <c r="BU3" t="n">
         <v>64794.27683459198</v>
       </c>
-      <c r="BU3" t="n">
-        <v>75137.10070382195</v>
-      </c>
       <c r="BV3" t="n">
+        <v>75137.10070382197</v>
+      </c>
+      <c r="BW3" t="n">
         <v>77434.88225229445</v>
       </c>
-      <c r="BW3" t="n">
-        <v>80408.53506490916</v>
-      </c>
       <c r="BX3" t="n">
-        <v>72536.49882266637</v>
+        <v>80408.53506490917</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>72536.49882266636</v>
       </c>
     </row>
     <row r="4">
@@ -1276,7 +1287,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>473551.7256051206</v>
+        <v>473551.7256051205</v>
       </c>
       <c r="C4" t="n">
         <v>289125.1070240645</v>
@@ -1288,7 +1299,7 @@
         <v>265290.3972004985</v>
       </c>
       <c r="F4" t="n">
-        <v>114124.8546349757</v>
+        <v>114124.8546349758</v>
       </c>
       <c r="G4" t="n">
         <v>103241.2458695452</v>
@@ -1297,7 +1308,7 @@
         <v>116074.2745859909</v>
       </c>
       <c r="I4" t="n">
-        <v>194741.9629844958</v>
+        <v>194741.9629844959</v>
       </c>
       <c r="J4" t="n">
         <v>213849.7020006684</v>
@@ -1363,7 +1374,7 @@
         <v>229548.699067146</v>
       </c>
       <c r="AE4" t="n">
-        <v>128192.2549721612</v>
+        <v>128192.2549721611</v>
       </c>
       <c r="AF4" t="n">
         <v>164266.3687433067</v>
@@ -1423,7 +1434,7 @@
         <v>341876.5071832517</v>
       </c>
       <c r="AY4" t="n">
-        <v>340809.411378612</v>
+        <v>340809.4113786119</v>
       </c>
       <c r="AZ4" t="n">
         <v>353206.8537280076</v>
@@ -1459,13 +1470,13 @@
         <v>104347.9899609492</v>
       </c>
       <c r="BK4" t="n">
-        <v>98800.7481366549</v>
+        <v>98800.74813665492</v>
       </c>
       <c r="BL4" t="n">
         <v>132525.3106954099</v>
       </c>
       <c r="BM4" t="n">
-        <v>89022.93597954437</v>
+        <v>89022.93597954439</v>
       </c>
       <c r="BN4" t="n">
         <v>115875.8940212374</v>
@@ -1474,30 +1485,33 @@
         <v>105254.0294787811</v>
       </c>
       <c r="BP4" t="n">
-        <v>58464.14349249625</v>
+        <v>58464.14349249626</v>
       </c>
       <c r="BQ4" t="n">
+        <v>185457.1202674733</v>
+      </c>
+      <c r="BR4" t="n">
         <v>176927.7799525312</v>
       </c>
-      <c r="BR4" t="n">
-        <v>149536.3129686544</v>
-      </c>
       <c r="BS4" t="n">
+        <v>149536.3129686545</v>
+      </c>
+      <c r="BT4" t="n">
         <v>148794.6844269141</v>
       </c>
-      <c r="BT4" t="n">
+      <c r="BU4" t="n">
         <v>104494.6003619383</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="BV4" t="n">
         <v>122672.8504187998</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="BW4" t="n">
         <v>124397.3728050634</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="BX4" t="n">
         <v>131096.9176983922</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="BY4" t="n">
         <v>120663.2753959248</v>
       </c>
     </row>
@@ -1709,27 +1723,30 @@
         <v>7300.91952348227</v>
       </c>
       <c r="BQ5" t="n">
+        <v>7090.977841208077</v>
+      </c>
+      <c r="BR5" t="n">
         <v>7295.643844303476</v>
       </c>
-      <c r="BR5" t="n">
+      <c r="BS5" t="n">
         <v>8870.156847249267</v>
       </c>
-      <c r="BS5" t="n">
+      <c r="BT5" t="n">
         <v>9727.164099679872</v>
       </c>
-      <c r="BT5" t="n">
+      <c r="BU5" t="n">
         <v>7407.232072230986</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="BV5" t="n">
         <v>8059.196314854126</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="BW5" t="n">
         <v>8058.01094541416</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="BX5" t="n">
         <v>8031.876061071963</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="BY5" t="n">
         <v>7106.518614424131</v>
       </c>
     </row>
@@ -1941,27 +1958,30 @@
         <v>9911.003395444626</v>
       </c>
       <c r="BQ6" t="n">
+        <v>13046.67396565851</v>
+      </c>
+      <c r="BR6" t="n">
         <v>13249.19716256196</v>
       </c>
-      <c r="BR6" t="n">
+      <c r="BS6" t="n">
         <v>15739.09937999126</v>
       </c>
-      <c r="BS6" t="n">
+      <c r="BT6" t="n">
         <v>17157.53058715043</v>
       </c>
-      <c r="BT6" t="n">
+      <c r="BU6" t="n">
         <v>12671.56603839952</v>
       </c>
-      <c r="BU6" t="n">
+      <c r="BV6" t="n">
         <v>13669.8226236754</v>
       </c>
-      <c r="BV6" t="n">
+      <c r="BW6" t="n">
         <v>13586.43830529653</v>
       </c>
-      <c r="BW6" t="n">
+      <c r="BX6" t="n">
         <v>13635.31195705756</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="BY6" t="n">
         <v>12215.30587910782</v>
       </c>
     </row>
@@ -2173,27 +2193,30 @@
         <v>15366.954286114</v>
       </c>
       <c r="BQ7" t="n">
+        <v>25726.6702483996</v>
+      </c>
+      <c r="BR7" t="n">
         <v>26714.12558138224</v>
       </c>
-      <c r="BR7" t="n">
+      <c r="BS7" t="n">
         <v>30963.38759736533</v>
       </c>
-      <c r="BS7" t="n">
+      <c r="BT7" t="n">
         <v>32869.87611887697</v>
       </c>
-      <c r="BT7" t="n">
+      <c r="BU7" t="n">
         <v>24488.04282112215</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="BV7" t="n">
         <v>26808.61193964766</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="BW7" t="n">
         <v>27600.8202719678</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="BX7" t="n">
         <v>27110.01043305021</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="BY7" t="n">
         <v>24344.8954868173</v>
       </c>
     </row>
@@ -2405,27 +2428,30 @@
         <v>31746.90135544375</v>
       </c>
       <c r="BQ8" t="n">
+        <v>66046.29449421521</v>
+      </c>
+      <c r="BR8" t="n">
         <v>66704.75722169633</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="BS8" t="n">
         <v>79159.61374579441</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="BT8" t="n">
         <v>85452.05509517266</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="BU8" t="n">
         <v>64971.29226966516</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="BV8" t="n">
         <v>76318.50865996671</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="BW8" t="n">
         <v>79502.08765670167</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="BX8" t="n">
         <v>77635.48292601698</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="BY8" t="n">
         <v>67920.31197821039</v>
       </c>
     </row>
@@ -2637,27 +2663,30 @@
         <v>746357.568074079</v>
       </c>
       <c r="BQ9" t="n">
+        <v>3989325.64061538</v>
+      </c>
+      <c r="BR9" t="n">
         <v>3563066.28214841</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="BS9" t="n">
         <v>2186908.808510384</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="BT9" t="n">
         <v>1526611.414481163</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="BU9" t="n">
         <v>1197000.573967651</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="BV9" t="n">
         <v>1459414.066163923</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="BW9" t="n">
         <v>1515763.911566187</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="BX9" t="n">
         <v>1527797.363900427</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="BY9" t="n">
         <v>1382972.910274663</v>
       </c>
     </row>

--- a/data/proteomics/protein_copy_statistical_top1000.xlsx
+++ b/data/proteomics/protein_copy_statistical_top1000.xlsx
@@ -1100,13 +1100,13 @@
         <v>37051.09863199265</v>
       </c>
       <c r="R3" t="n">
-        <v>40838.82650441666</v>
+        <v>40838.82650441667</v>
       </c>
       <c r="S3" t="n">
         <v>39849.08103696295</v>
       </c>
       <c r="T3" t="n">
-        <v>40192.75463917517</v>
+        <v>40192.75463917518</v>
       </c>
       <c r="U3" t="n">
         <v>68188.02035978963</v>
@@ -1154,13 +1154,13 @@
         <v>50109.96282314113</v>
       </c>
       <c r="AJ3" t="n">
-        <v>58125.27215142744</v>
+        <v>58125.27215142745</v>
       </c>
       <c r="AK3" t="n">
         <v>72327.59058242066</v>
       </c>
       <c r="AL3" t="n">
-        <v>62104.85691750223</v>
+        <v>62104.85691750222</v>
       </c>
       <c r="AM3" t="n">
         <v>58413.23388771783</v>
@@ -1193,7 +1193,7 @@
         <v>56218.47606892</v>
       </c>
       <c r="AW3" t="n">
-        <v>110958.078901428</v>
+        <v>110958.0789014279</v>
       </c>
       <c r="AX3" t="n">
         <v>114227.8779710944</v>
@@ -1205,10 +1205,10 @@
         <v>101949.8285084604</v>
       </c>
       <c r="BA3" t="n">
-        <v>120801.117372055</v>
+        <v>120801.1173720551</v>
       </c>
       <c r="BB3" t="n">
-        <v>76215.01799274819</v>
+        <v>76215.01799274821</v>
       </c>
       <c r="BC3" t="n">
         <v>122161.0464563577</v>
@@ -1302,13 +1302,13 @@
         <v>114124.8546349758</v>
       </c>
       <c r="G4" t="n">
-        <v>103241.2458695452</v>
+        <v>103241.2458695453</v>
       </c>
       <c r="H4" t="n">
         <v>116074.2745859909</v>
       </c>
       <c r="I4" t="n">
-        <v>194741.9629844959</v>
+        <v>194741.9629844958</v>
       </c>
       <c r="J4" t="n">
         <v>213849.7020006684</v>
@@ -1365,7 +1365,7 @@
         <v>304067.2123832731</v>
       </c>
       <c r="AB4" t="n">
-        <v>358420.0042492592</v>
+        <v>358420.0042492593</v>
       </c>
       <c r="AC4" t="n">
         <v>358873.2615219346</v>
@@ -1392,7 +1392,7 @@
         <v>176027.7988613566</v>
       </c>
       <c r="AK4" t="n">
-        <v>232378.0488984838</v>
+        <v>232378.0488984839</v>
       </c>
       <c r="AL4" t="n">
         <v>187014.9221617106</v>
@@ -1407,7 +1407,7 @@
         <v>151615.8301893591</v>
       </c>
       <c r="AP4" t="n">
-        <v>140484.4375324662</v>
+        <v>140484.4375324663</v>
       </c>
       <c r="AQ4" t="n">
         <v>193950.9127080156</v>
@@ -1428,7 +1428,7 @@
         <v>116774.1687569073</v>
       </c>
       <c r="AW4" t="n">
-        <v>323028.6516446971</v>
+        <v>323028.6516446972</v>
       </c>
       <c r="AX4" t="n">
         <v>341876.5071832517</v>
@@ -1443,7 +1443,7 @@
         <v>302463.3125554243</v>
       </c>
       <c r="BB4" t="n">
-        <v>179555.3409466877</v>
+        <v>179555.3409466878</v>
       </c>
       <c r="BC4" t="n">
         <v>297502.1754728873</v>
@@ -1452,13 +1452,13 @@
         <v>147978.1554881051</v>
       </c>
       <c r="BE4" t="n">
-        <v>198920.2825271324</v>
+        <v>198920.2825271325</v>
       </c>
       <c r="BF4" t="n">
         <v>194530.08111154</v>
       </c>
       <c r="BG4" t="n">
-        <v>201584.3046314215</v>
+        <v>201584.3046314216</v>
       </c>
       <c r="BH4" t="n">
         <v>196143.1933133978</v>
@@ -1775,7 +1775,7 @@
         <v>2338.559765773605</v>
       </c>
       <c r="H6" t="n">
-        <v>2437.673375984385</v>
+        <v>2437.673375984386</v>
       </c>
       <c r="I6" t="n">
         <v>3225.853971425305</v>
@@ -1814,10 +1814,10 @@
         <v>2848.23995218532</v>
       </c>
       <c r="U6" t="n">
-        <v>4000.688118024896</v>
+        <v>4000.688118024895</v>
       </c>
       <c r="V6" t="n">
-        <v>3995.708190424611</v>
+        <v>3995.70819042461</v>
       </c>
       <c r="W6" t="n">
         <v>3681.603186221125</v>
@@ -1865,7 +1865,7 @@
         <v>4631.824013074665</v>
       </c>
       <c r="AL6" t="n">
-        <v>4086.545992520971</v>
+        <v>4086.54599252097</v>
       </c>
       <c r="AM6" t="n">
         <v>4188.61961438338</v>
@@ -1883,7 +1883,7 @@
         <v>3787.67072074853</v>
       </c>
       <c r="AR6" t="n">
-        <v>3225.514541765505</v>
+        <v>3225.514541765506</v>
       </c>
       <c r="AS6" t="n">
         <v>4502.004219242091</v>
@@ -1925,7 +1925,7 @@
         <v>10315.87191092336</v>
       </c>
       <c r="BF6" t="n">
-        <v>10179.24926280669</v>
+        <v>10179.2492628067</v>
       </c>
       <c r="BG6" t="n">
         <v>10962.99629254136</v>
@@ -1995,13 +1995,13 @@
         <v>13389.96439458389</v>
       </c>
       <c r="C7" t="n">
-        <v>16442.70140861564</v>
+        <v>16442.70140861565</v>
       </c>
       <c r="D7" t="n">
         <v>17299.19823943009</v>
       </c>
       <c r="E7" t="n">
-        <v>17401.07496193695</v>
+        <v>17401.07496193696</v>
       </c>
       <c r="F7" t="n">
         <v>6420.7192586746</v>
@@ -2112,7 +2112,7 @@
         <v>8939.7311000503</v>
       </c>
       <c r="AP7" t="n">
-        <v>6640.85345067782</v>
+        <v>6640.853450677821</v>
       </c>
       <c r="AQ7" t="n">
         <v>8225.940231752098</v>
@@ -2148,10 +2148,10 @@
         <v>33956.95077590895</v>
       </c>
       <c r="BB7" t="n">
-        <v>21910.83972995547</v>
+        <v>21910.83972995546</v>
       </c>
       <c r="BC7" t="n">
-        <v>36528.54552456376</v>
+        <v>36528.54552456377</v>
       </c>
       <c r="BD7" t="n">
         <v>18743.13274653286</v>
@@ -2308,7 +2308,7 @@
         <v>37375.69582466281</v>
       </c>
       <c r="AC8" t="n">
-        <v>38463.62248934701</v>
+        <v>38463.622489347</v>
       </c>
       <c r="AD8" t="n">
         <v>34623.35397996476</v>
@@ -2332,10 +2332,10 @@
         <v>31482.892069442</v>
       </c>
       <c r="AK8" t="n">
-        <v>37549.47926332405</v>
+        <v>37549.47926332404</v>
       </c>
       <c r="AL8" t="n">
-        <v>33928.98227626436</v>
+        <v>33928.98227626435</v>
       </c>
       <c r="AM8" t="n">
         <v>32445.7307693277</v>
@@ -2377,7 +2377,7 @@
         <v>47102.71896187135</v>
       </c>
       <c r="AZ8" t="n">
-        <v>43830.33723661795</v>
+        <v>43830.33723661796</v>
       </c>
       <c r="BA8" t="n">
         <v>97900.59145410832</v>

--- a/data/proteomics/protein_copy_statistical_top1000.xlsx
+++ b/data/proteomics/protein_copy_statistical_top1000.xlsx
@@ -425,48 +425,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>C-lim rep1 prot (fmol mgDW-1)</t>
+          <t>ref_glc_mm_rich_aerobic(mmol/gDW)_x</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>C-lim rep2 prot (fmol mgDW-1)</t>
+          <t>maltose(mmol/gDW)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>C/N=115 rep1 prot (fmol mgDW-1)</t>
+          <t>oleate(mmol/gDW)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>C/N=115 rep2 prot (fmol mgDW-1)</t>
+          <t>fructose(mmol/gDW)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>C/N=30 rep1 prot (fmol mgDW-1)</t>
+          <t>sucrose(mmol/gDW)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>C/N=30 rep2 prot (fmol mgDW-1)</t>
+          <t>trehalose(mmol/gDW)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>C/N=50 rep1 prot (fmol mgDW-1)</t>
+          <t>lactate(mmol/gDW)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>C/N=50 rep2 prot (fmol mgDW-1)</t>
+          <t>acetate(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>pryuvate(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>glycerol(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>galactose(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>raffinose(mmol/gDW)</t>
         </is>
       </c>
     </row>
@@ -500,6 +520,18 @@
       <c r="I2" t="n">
         <v>1000</v>
       </c>
+      <c r="J2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -508,28 +540,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48548.01885759088</v>
+        <v>89062.02900260568</v>
       </c>
       <c r="C3" t="n">
-        <v>49076.8414643935</v>
+        <v>90101.44000503165</v>
       </c>
       <c r="D3" t="n">
-        <v>26873.12197155616</v>
+        <v>96854.03285125572</v>
       </c>
       <c r="E3" t="n">
-        <v>28099.5886312816</v>
+        <v>94457.19510634952</v>
       </c>
       <c r="F3" t="n">
-        <v>37844.70691562299</v>
+        <v>93152.28167818206</v>
       </c>
       <c r="G3" t="n">
-        <v>38944.17841656582</v>
+        <v>88158.12718218745</v>
       </c>
       <c r="H3" t="n">
-        <v>22621.78541096393</v>
+        <v>89381.54119445605</v>
       </c>
       <c r="I3" t="n">
-        <v>23599.96847472253</v>
+        <v>111204.999221424</v>
+      </c>
+      <c r="J3" t="n">
+        <v>101383.8587757529</v>
+      </c>
+      <c r="K3" t="n">
+        <v>92404.16145146871</v>
+      </c>
+      <c r="L3" t="n">
+        <v>77364.13511731174</v>
+      </c>
+      <c r="M3" t="n">
+        <v>76779.49436118959</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +583,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>168398.1863507545</v>
+        <v>276705.8703409182</v>
       </c>
       <c r="C4" t="n">
-        <v>152107.3869686093</v>
+        <v>235844.3691802917</v>
       </c>
       <c r="D4" t="n">
-        <v>74747.95952725847</v>
+        <v>256839.1586328733</v>
       </c>
       <c r="E4" t="n">
-        <v>77489.70600159597</v>
+        <v>303522.404038647</v>
       </c>
       <c r="F4" t="n">
-        <v>109680.1570831819</v>
+        <v>302646.485228717</v>
       </c>
       <c r="G4" t="n">
-        <v>105913.8298805153</v>
+        <v>224894.6025179674</v>
       </c>
       <c r="H4" t="n">
-        <v>62291.45714803164</v>
+        <v>225430.4516058913</v>
       </c>
       <c r="I4" t="n">
-        <v>68020.85248590687</v>
+        <v>309924.7517149917</v>
+      </c>
+      <c r="J4" t="n">
+        <v>300498.114570479</v>
+      </c>
+      <c r="K4" t="n">
+        <v>238538.4729674571</v>
+      </c>
+      <c r="L4" t="n">
+        <v>286538.3824025185</v>
+      </c>
+      <c r="M4" t="n">
+        <v>256929.2838757988</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +626,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2604.148382173297</v>
+        <v>4466.766246003109</v>
       </c>
       <c r="C5" t="n">
-        <v>2759.164392360652</v>
+        <v>4421.530275530009</v>
       </c>
       <c r="D5" t="n">
-        <v>1340.636972667482</v>
+        <v>4852.60400171739</v>
       </c>
       <c r="E5" t="n">
-        <v>1706.177404122524</v>
+        <v>4477.84777579591</v>
       </c>
       <c r="F5" t="n">
-        <v>2186.368817103923</v>
+        <v>4653.473496658243</v>
       </c>
       <c r="G5" t="n">
-        <v>2299.714886536085</v>
+        <v>4875.714087512352</v>
       </c>
       <c r="H5" t="n">
-        <v>1346.73545294571</v>
+        <v>4799.42148568716</v>
       </c>
       <c r="I5" t="n">
-        <v>1381.011362066836</v>
+        <v>4852.291779119411</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5029.373510375292</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5230.576827930286</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4583.52085475708</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4343.062933130394</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +669,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4323.187088830372</v>
+        <v>7583.179833629523</v>
       </c>
       <c r="C6" t="n">
-        <v>4792.268442953651</v>
+        <v>7705.257432622958</v>
       </c>
       <c r="D6" t="n">
-        <v>2445.694642135311</v>
+        <v>8318.969541618622</v>
       </c>
       <c r="E6" t="n">
-        <v>2994.955719548667</v>
+        <v>7911.487875853649</v>
       </c>
       <c r="F6" t="n">
-        <v>3578.198576226665</v>
+        <v>7922.844200489174</v>
       </c>
       <c r="G6" t="n">
-        <v>3977.66840151467</v>
+        <v>8427.832982481199</v>
       </c>
       <c r="H6" t="n">
-        <v>2311.011568638321</v>
+        <v>8199.858264315415</v>
       </c>
       <c r="I6" t="n">
-        <v>2446.67290233451</v>
+        <v>8614.122202285856</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8770.851122319431</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8605.185852087463</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7461.186885505573</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7178.439500410393</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +712,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8503.232678299306</v>
+        <v>14809.08405837282</v>
       </c>
       <c r="C7" t="n">
-        <v>9078.262373737878</v>
+        <v>18033.36240866197</v>
       </c>
       <c r="D7" t="n">
-        <v>5019.075006750934</v>
+        <v>18348.04606612602</v>
       </c>
       <c r="E7" t="n">
-        <v>6209.175651587482</v>
+        <v>15534.60128983051</v>
       </c>
       <c r="F7" t="n">
-        <v>7101.106955093064</v>
+        <v>15518.03783936034</v>
       </c>
       <c r="G7" t="n">
-        <v>7786.312728397102</v>
+        <v>18413.23785794818</v>
       </c>
       <c r="H7" t="n">
-        <v>4751.266181633289</v>
+        <v>17869.46442402063</v>
       </c>
       <c r="I7" t="n">
-        <v>4964.809969413138</v>
+        <v>18842.17553419524</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18039.89069266979</v>
+      </c>
+      <c r="K7" t="n">
+        <v>18034.2121570603</v>
+      </c>
+      <c r="L7" t="n">
+        <v>14332.44107385187</v>
+      </c>
+      <c r="M7" t="n">
+        <v>13675.61473580465</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +755,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24376.71691919952</v>
+        <v>44061.78150411177</v>
       </c>
       <c r="C8" t="n">
-        <v>26942.75568557541</v>
+        <v>55375.63500668943</v>
       </c>
       <c r="D8" t="n">
-        <v>15636.9255705624</v>
+        <v>59500.45153850355</v>
       </c>
       <c r="E8" t="n">
-        <v>18041.00124122589</v>
+        <v>43554.77528704339</v>
       </c>
       <c r="F8" t="n">
-        <v>21246.71865420777</v>
+        <v>44598.0138179108</v>
       </c>
       <c r="G8" t="n">
-        <v>23406.12560210979</v>
+        <v>57644.29696555629</v>
       </c>
       <c r="H8" t="n">
-        <v>14070.87644201444</v>
+        <v>57419.63754724183</v>
       </c>
       <c r="I8" t="n">
-        <v>15013.37172085309</v>
+        <v>54617.01279702976</v>
+      </c>
+      <c r="J8" t="n">
+        <v>60695.8389664479</v>
+      </c>
+      <c r="K8" t="n">
+        <v>53458.79675728663</v>
+      </c>
+      <c r="L8" t="n">
+        <v>41272.63425310593</v>
+      </c>
+      <c r="M8" t="n">
+        <v>39662.3256685274</v>
       </c>
     </row>
     <row r="9">
@@ -694,28 +798,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3532728.342374335</v>
+        <v>2827568.866170935</v>
       </c>
       <c r="C9" t="n">
-        <v>2873851.595377475</v>
+        <v>3441293.778590984</v>
       </c>
       <c r="D9" t="n">
-        <v>942560.9738540711</v>
+        <v>2997519.452074238</v>
       </c>
       <c r="E9" t="n">
-        <v>990764.0790722463</v>
+        <v>3474572.365462308</v>
       </c>
       <c r="F9" t="n">
-        <v>1481068.682882923</v>
+        <v>3766905.59001234</v>
       </c>
       <c r="G9" t="n">
-        <v>1285386.303692142</v>
+        <v>2753403.630072502</v>
       </c>
       <c r="H9" t="n">
-        <v>674599.3665497858</v>
+        <v>2173211.290130805</v>
       </c>
       <c r="I9" t="n">
-        <v>1062372.807385358</v>
+        <v>3039979.376189653</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6004868.809911354</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2247437.265527637</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5375654.536827597</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4239740.357313359</v>
       </c>
     </row>
   </sheetData>

--- a/data/proteomics/protein_copy_statistical_top1000.xlsx
+++ b/data/proteomics/protein_copy_statistical_top1000.xlsx
@@ -425,68 +425,388 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:BY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ref_glc_mm_rich_aerobic(mmol/gDW)_x</t>
+          <t>Glucose_phase(mmol/gDW)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>maltose(mmol/gDW)</t>
+          <t>Diauxic_shift(mmol/gDW)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>oleate(mmol/gDW)</t>
+          <t>Ethanol_phase(mmol/gDW)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>fructose(mmol/gDW)</t>
+          <t>mmol/gDW_carl</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>sucrose(mmol/gDW)</t>
+          <t>prot.1</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>trehalose(mmol/gDW)</t>
+          <t>prot.2</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>lactate(mmol/gDW)</t>
+          <t>prot.3</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>acetate(mmol/gDW)</t>
+          <t>prot.4</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>pryuvate(mmol/gDW)</t>
+          <t>prot.5</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>glycerol(mmol/gDW)</t>
+          <t>prot.6</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>galactose(mmol/gDW)</t>
+          <t>prot.7</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>raffinose(mmol/gDW)</t>
+          <t>prot.8</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>prot.9</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>prot.10</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>prot.11</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>prot.12</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>prot.13</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>prot.14</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>prot.15</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>prot.16</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>prot.17</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>prot.18</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>prot.19</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>prot.20</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>prot.21</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>prot.22</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>prot.23</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>prot.24</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>prot.25</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>prot.26</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>prot.27</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>prot.28</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>prot.29</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>prot.30</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>prot.31</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>prot.32</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>prot.33</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>prot.34</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>prot.35</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>prot.36</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>prot.37</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>prot.38</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>prot.39</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>prot.40</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>prot.41</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>prot.42</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>mmol/gDW_Tyler_D0.1</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Min_ave_aerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Rich_ave_aerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Min_ave_anaerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Rich_ave_anaerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_REF_CN4_D=0.1</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_CN22_D=0.1</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_CN38_D=0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_CN75_D=0.1</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep1_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep2_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep3_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep4_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>molecular/cell_paxdb</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghaemmaghami et al. 2003 - Copy </t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Kulak et al. 2014 - Copy</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Copy number - Glucose</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Copy number - Galactose</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Copy number - Glycerol</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Mean molecules per cell_cell_system_2018</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Median molecules per cell_cell_system_2018</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.027_M</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.044_M</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.102_M</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.152_M</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.214_M</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.254_M</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.284_M</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.334_M</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.379_M</t>
         </is>
       </c>
     </row>
@@ -532,6 +852,198 @@
       <c r="M2" t="n">
         <v>1000</v>
       </c>
+      <c r="N2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -540,40 +1052,232 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89062.02900260568</v>
+        <v>118666.5729440651</v>
       </c>
       <c r="C3" t="n">
-        <v>90101.44000503165</v>
+        <v>106756.1964861159</v>
       </c>
       <c r="D3" t="n">
-        <v>96854.03285125572</v>
+        <v>92809.76170128527</v>
       </c>
       <c r="E3" t="n">
-        <v>94457.19510634952</v>
+        <v>105064.9080032164</v>
       </c>
       <c r="F3" t="n">
-        <v>93152.28167818206</v>
+        <v>38526.59640408488</v>
       </c>
       <c r="G3" t="n">
-        <v>88158.12718218745</v>
+        <v>34693.48548003553</v>
       </c>
       <c r="H3" t="n">
-        <v>89381.54119445605</v>
+        <v>37168.14778022456</v>
       </c>
       <c r="I3" t="n">
-        <v>111204.999221424</v>
+        <v>55166.83707125369</v>
       </c>
       <c r="J3" t="n">
-        <v>101383.8587757529</v>
+        <v>58873.38541922928</v>
       </c>
       <c r="K3" t="n">
-        <v>92404.16145146871</v>
+        <v>49578.10471780638</v>
       </c>
       <c r="L3" t="n">
-        <v>77364.13511731174</v>
+        <v>28609.71781178535</v>
       </c>
       <c r="M3" t="n">
-        <v>76779.49436118959</v>
+        <v>30222.15759491802</v>
+      </c>
+      <c r="N3" t="n">
+        <v>39960.17206208715</v>
+      </c>
+      <c r="O3" t="n">
+        <v>43292.15446450197</v>
+      </c>
+      <c r="P3" t="n">
+        <v>37040.0009527303</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>37051.09863199265</v>
+      </c>
+      <c r="R3" t="n">
+        <v>40838.82650441667</v>
+      </c>
+      <c r="S3" t="n">
+        <v>39849.08103696295</v>
+      </c>
+      <c r="T3" t="n">
+        <v>40192.75463917518</v>
+      </c>
+      <c r="U3" t="n">
+        <v>68188.02035978963</v>
+      </c>
+      <c r="V3" t="n">
+        <v>68302.52225944481</v>
+      </c>
+      <c r="W3" t="n">
+        <v>64553.2746363598</v>
+      </c>
+      <c r="X3" t="n">
+        <v>84923.25512229696</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>89691.19445015976</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>89384.77250020954</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>76682.69396234934</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>92758.04731701875</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>95248.41993361684</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>73110.99248757317</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>43122.94808525473</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>53698.23620652136</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>30860.52910408555</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>50473.06163056983</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>50109.96282314113</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>58125.27215142745</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>72327.59058242066</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>62104.85691750222</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>58413.23388771783</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>52608.21437278811</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>55482.51196158198</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>46106.19990032677</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>60214.95839389114</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>51409.28057582907</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>70178.35267045889</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>67282.09186947322</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>65420.9956137284</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>56218.47606892</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>110958.0789014279</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>114227.8779710944</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>97932.30695506986</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>101949.8285084604</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>120801.1173720551</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>76215.01799274821</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>122161.0464563577</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>62628.56142679702</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>84972.93904289401</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>83545.98291395989</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>86777.87373623672</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>84854.79851132451</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>69468.56</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>41362.54604555698</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>50762.72378199999</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>60220.1</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>46466.519</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>56764.487</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>48056.15967633893</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>30790.68569767767</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>70924.98469309551</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>72950.20005716999</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>79867.75266700536</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>87516.54554463542</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>64794.27683459198</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>75137.10070382197</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>77434.88225229445</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>80408.53506490917</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>72536.49882266636</v>
       </c>
     </row>
     <row r="4">
@@ -583,40 +1287,232 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>276705.8703409182</v>
+        <v>473551.7256051205</v>
       </c>
       <c r="C4" t="n">
-        <v>235844.3691802917</v>
+        <v>289125.1070240645</v>
       </c>
       <c r="D4" t="n">
-        <v>256839.1586328733</v>
+        <v>291264.2097555604</v>
       </c>
       <c r="E4" t="n">
-        <v>303522.404038647</v>
+        <v>265290.3972004985</v>
       </c>
       <c r="F4" t="n">
-        <v>302646.485228717</v>
+        <v>114124.8546349758</v>
       </c>
       <c r="G4" t="n">
-        <v>224894.6025179674</v>
+        <v>103241.2458695453</v>
       </c>
       <c r="H4" t="n">
-        <v>225430.4516058913</v>
+        <v>116074.2745859909</v>
       </c>
       <c r="I4" t="n">
-        <v>309924.7517149917</v>
+        <v>194741.9629844958</v>
       </c>
       <c r="J4" t="n">
-        <v>300498.114570479</v>
+        <v>213849.7020006684</v>
       </c>
       <c r="K4" t="n">
-        <v>238538.4729674571</v>
+        <v>165591.2353694275</v>
       </c>
       <c r="L4" t="n">
-        <v>286538.3824025185</v>
+        <v>88033.84215074276</v>
       </c>
       <c r="M4" t="n">
-        <v>256929.2838757988</v>
+        <v>91808.1369340705</v>
+      </c>
+      <c r="N4" t="n">
+        <v>116068.9523166056</v>
+      </c>
+      <c r="O4" t="n">
+        <v>121835.6145666198</v>
+      </c>
+      <c r="P4" t="n">
+        <v>108909.6174784841</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>105925.601315764</v>
+      </c>
+      <c r="R4" t="n">
+        <v>111501.1654192605</v>
+      </c>
+      <c r="S4" t="n">
+        <v>109493.907562838</v>
+      </c>
+      <c r="T4" t="n">
+        <v>116261.8476219478</v>
+      </c>
+      <c r="U4" t="n">
+        <v>199141.7879318864</v>
+      </c>
+      <c r="V4" t="n">
+        <v>194023.0141419295</v>
+      </c>
+      <c r="W4" t="n">
+        <v>181534.6670459086</v>
+      </c>
+      <c r="X4" t="n">
+        <v>242606.7664132215</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>261549.1295274351</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>254268.5662500033</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>304067.2123832731</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>358420.0042492593</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>358873.2615219346</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>229548.699067146</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>128192.2549721611</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>164266.3687433067</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>84467.52871055336</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>137526.5194625088</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>136453.6267988162</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>176027.7988613566</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>232378.0488984839</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>187014.9221617106</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>171566.6002991211</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>146758.7569109736</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>151615.8301893591</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>140484.4375324663</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>193950.9127080156</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>154324.4473354669</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>202006.3943943077</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>199344.6501770437</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>192631.4129956177</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>116774.1687569073</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>323028.6516446972</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>341876.5071832517</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>340809.4113786119</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>353206.8537280076</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>302463.3125554243</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>179555.3409466878</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>297502.1754728873</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>147978.1554881051</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>198920.2825271325</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>194530.08111154</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>201584.3046314216</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>196143.1933133978</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>130266.9026416543</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>104347.9899609492</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>98800.74813665492</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>132525.3106954099</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>89022.93597954439</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>115875.8940212374</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>105254.0294787811</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>58464.14349249626</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>185457.1202674733</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>176927.7799525312</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>149536.3129686545</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>148794.6844269141</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>104494.6003619383</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>122672.8504187998</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>124397.3728050634</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>131096.9176983922</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>120663.2753959248</v>
       </c>
     </row>
     <row r="5">
@@ -626,40 +1522,232 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4466.766246003109</v>
+        <v>3107.197480626479</v>
       </c>
       <c r="C5" t="n">
-        <v>4421.530275530009</v>
+        <v>3907.107878840001</v>
       </c>
       <c r="D5" t="n">
-        <v>4852.60400171739</v>
+        <v>4023.513085708761</v>
       </c>
       <c r="E5" t="n">
-        <v>4477.84777579591</v>
+        <v>5366.744646409529</v>
       </c>
       <c r="F5" t="n">
-        <v>4653.473496658243</v>
+        <v>1354.85263643356</v>
       </c>
       <c r="G5" t="n">
-        <v>4875.714087512352</v>
+        <v>1226.22003817918</v>
       </c>
       <c r="H5" t="n">
-        <v>4799.42148568716</v>
+        <v>1242.54606769128</v>
       </c>
       <c r="I5" t="n">
-        <v>4852.291779119411</v>
+        <v>1647.46931965286</v>
       </c>
       <c r="J5" t="n">
-        <v>5029.373510375292</v>
+        <v>1754.4299178406</v>
       </c>
       <c r="K5" t="n">
-        <v>5230.576827930286</v>
+        <v>1512.36513096614</v>
       </c>
       <c r="L5" t="n">
-        <v>4583.52085475708</v>
+        <v>1072.82666127318</v>
       </c>
       <c r="M5" t="n">
-        <v>4343.062933130394</v>
+        <v>1124.29329514348</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1210.54020989088</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1599.02521564676</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1336.96730381742</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1401.11828650486</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1493.42438515688</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1478.21098040352</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1509.01024488346</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2117.16119319826</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2156.7466912376</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1999.48944583608</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2268.40856990748</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2368.49392485156</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2468.63892329714</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2103.86415470132</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2560.43107152822</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2494.98511900176</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2339.48151860412</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1407.899240165</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1735.10649525422</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1085.74712084124</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1851.14105649176</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1877.98348612886</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2011.43145757906</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2405.37930226726</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2051.90012808814</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2218.37498126728</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1959.3324248564</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2087.26923263166</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1512.24161900306</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1973.54623584382</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1593.12978339636</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2239.4271751489</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2247.33742477794</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2066.88187568082</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4165.453600000001</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4252.297358456579</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4702.352021166066</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4035.330859904059</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4348.50614279469</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8630.381030457032</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5798.559819150278</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>9185.706454255054</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4808.572736454925</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5876.131610122532</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5650.116368655028</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6187.381591652433</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>5992.074201495198</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>10880</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>6024.12188755227</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4998.245</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>4802</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>4045</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5112</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>9290.70616454881</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>7300.91952348227</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>7090.977841208077</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>7295.643844303476</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>8870.156847249267</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>9727.164099679872</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>7407.232072230986</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>8059.196314854126</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>8058.01094541416</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>8031.876061071963</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>7106.518614424131</v>
       </c>
     </row>
     <row r="6">
@@ -669,40 +1757,232 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7583.179833629523</v>
+        <v>6025.959491685639</v>
       </c>
       <c r="C6" t="n">
-        <v>7705.257432622958</v>
+        <v>7216.527869111726</v>
       </c>
       <c r="D6" t="n">
-        <v>8318.969541618622</v>
+        <v>7284.263594162116</v>
       </c>
       <c r="E6" t="n">
-        <v>7911.487875853649</v>
+        <v>8825.138567073458</v>
       </c>
       <c r="F6" t="n">
-        <v>7922.844200489174</v>
+        <v>2544.255144175745</v>
       </c>
       <c r="G6" t="n">
-        <v>8427.832982481199</v>
+        <v>2338.559765773605</v>
       </c>
       <c r="H6" t="n">
-        <v>8199.858264315415</v>
+        <v>2437.673375984386</v>
       </c>
       <c r="I6" t="n">
-        <v>8614.122202285856</v>
+        <v>3225.853971425305</v>
       </c>
       <c r="J6" t="n">
-        <v>8770.851122319431</v>
+        <v>3471.32282981583</v>
       </c>
       <c r="K6" t="n">
-        <v>8605.185852087463</v>
+        <v>2998.3552588275</v>
       </c>
       <c r="L6" t="n">
-        <v>7461.186885505573</v>
+        <v>2019.981178131566</v>
       </c>
       <c r="M6" t="n">
-        <v>7178.439500410393</v>
+        <v>2153.63301545458</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2379.8967468133</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3065.38373333841</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2580.319726789365</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2647.60000512359</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2879.78136112634</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2800.24721540025</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2848.23995218532</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4000.688118024895</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3995.70819042461</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3681.603186221125</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4425.33979935234</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4460.887174152475</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4529.85789260455</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4132.282241039755</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4817.43531536938</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5016.26149826538</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4563.5995094052</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2729.88574888491</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3478.5146784608</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2125.095596390085</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3553.65047436036</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3605.545815814746</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3922.537465856625</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>4631.824013074665</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4086.54599252097</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>4188.61961438338</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>3831.02181233167</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>3938.190293079625</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2980.824811700615</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3787.67072074853</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3225.514541765505</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4502.004219242091</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4418.12505754664</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4232.98804714863</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10983.90443333333</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7515.815423920358</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>8120.698926603831</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7250.541152611132</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7650.553751903668</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>16494.61059862406</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10875.52250551388</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>17509.36708087136</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9064.389944347275</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>10315.87191092336</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>10179.2492628067</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>10962.99629254136</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>10720.83894146489</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>16480</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>7864.32899943488</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>8484.61925</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>8615.75</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>7150.75</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>9553.75</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>13023.41370792537</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>9911.003395444628</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>13046.67396565851</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>13249.19716256196</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>15739.09937999126</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>17157.53058715043</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>12671.56603839952</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>13669.8226236754</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>13586.43830529653</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>13635.31195705756</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>12215.30587910782</v>
       </c>
     </row>
     <row r="7">
@@ -712,40 +1992,232 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14809.08405837282</v>
+        <v>13389.96439458389</v>
       </c>
       <c r="C7" t="n">
-        <v>18033.36240866197</v>
+        <v>16442.70140861565</v>
       </c>
       <c r="D7" t="n">
-        <v>18348.04606612602</v>
+        <v>17299.19823943009</v>
       </c>
       <c r="E7" t="n">
-        <v>15534.60128983051</v>
+        <v>17401.07496193696</v>
       </c>
       <c r="F7" t="n">
-        <v>15518.03783936034</v>
+        <v>6420.7192586746</v>
       </c>
       <c r="G7" t="n">
-        <v>18413.23785794818</v>
+        <v>5737.126536054981</v>
       </c>
       <c r="H7" t="n">
-        <v>17869.46442402063</v>
+        <v>5994.483038210481</v>
       </c>
       <c r="I7" t="n">
-        <v>18842.17553419524</v>
+        <v>7906.828973420301</v>
       </c>
       <c r="J7" t="n">
-        <v>18039.89069266979</v>
+        <v>7902.751264474</v>
       </c>
       <c r="K7" t="n">
-        <v>18034.2121570603</v>
+        <v>6732.8812484846</v>
       </c>
       <c r="L7" t="n">
-        <v>14332.44107385187</v>
+        <v>4620.152265865951</v>
       </c>
       <c r="M7" t="n">
-        <v>13675.61473580465</v>
+        <v>4914.705515834179</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5723.4884095466</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6990.654033310311</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5860.481511253491</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6143.514517706831</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6433.232892404891</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6173.20062578461</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6443.91032254563</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9063.086893854401</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9218.0607158904</v>
+      </c>
+      <c r="W7" t="n">
+        <v>8505.339053760999</v>
+      </c>
+      <c r="X7" t="n">
+        <v>9920.5704200933</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>10229.4795468976</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>10933.2732874068</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9295.9143551659</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11337.8507863621</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11560.1850707354</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>10127.1748006924</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>6223.31277002523</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>7690.083883725761</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4763.82346389081</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>8050.60466639</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>8334.779447164499</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>8610.890567472601</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>10410.6485873027</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>9461.3718331033</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>9378.8632367914</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>8503.7749141895</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>8939.7311000503</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>6640.853450677821</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8225.940231752098</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>7216.70717006184</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10226.2691096632</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10042.5063109866</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9575.0604508053</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>26190.681</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>15609.95655560721</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>16276.91132421246</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>16208.70304617097</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16242.13310949606</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>33956.95077590895</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>21910.83972995546</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>36528.54552456377</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>18743.13274653286</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>20895.1139454473</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>20645.72522610265</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>22114.81404777861</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>21761.65913837581</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>28840</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>13112.9007092155</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>17275.445</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>16104.5</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>14002</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>17878</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>20879.48415664675</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>15366.954286114</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>25726.6702483996</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>26714.12558138224</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>30963.38759736533</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>32869.87611887697</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>24488.04282112215</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>26808.61193964766</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>27600.8202719678</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>27110.01043305021</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>24344.8954868173</v>
       </c>
     </row>
     <row r="8">
@@ -755,40 +2227,232 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44061.78150411177</v>
+        <v>44031.08146310747</v>
       </c>
       <c r="C8" t="n">
-        <v>55375.63500668943</v>
+        <v>55126.11925017054</v>
       </c>
       <c r="D8" t="n">
-        <v>59500.45153850355</v>
+        <v>61120.08269009536</v>
       </c>
       <c r="E8" t="n">
-        <v>43554.77528704339</v>
+        <v>52033.9561581314</v>
       </c>
       <c r="F8" t="n">
-        <v>44598.0138179108</v>
+        <v>19652.3192507939</v>
       </c>
       <c r="G8" t="n">
-        <v>57644.29696555629</v>
+        <v>17467.5547634071</v>
       </c>
       <c r="H8" t="n">
-        <v>57419.63754724183</v>
+        <v>18635.8970836291</v>
       </c>
       <c r="I8" t="n">
-        <v>54617.01279702976</v>
+        <v>24381.28550837155</v>
       </c>
       <c r="J8" t="n">
-        <v>60695.8389664479</v>
+        <v>23963.5155226302</v>
       </c>
       <c r="K8" t="n">
-        <v>53458.79675728663</v>
+        <v>22941.4389714378</v>
       </c>
       <c r="L8" t="n">
-        <v>41272.63425310593</v>
+        <v>15122.83299964635</v>
       </c>
       <c r="M8" t="n">
-        <v>39662.3256685274</v>
+        <v>15964.7985689247</v>
+      </c>
+      <c r="N8" t="n">
+        <v>21954.4964749759</v>
+      </c>
+      <c r="O8" t="n">
+        <v>22969.6396795448</v>
+      </c>
+      <c r="P8" t="n">
+        <v>19710.8129657384</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>19772.9461126593</v>
+      </c>
+      <c r="R8" t="n">
+        <v>22192.36180382045</v>
+      </c>
+      <c r="S8" t="n">
+        <v>21972.5679822275</v>
+      </c>
+      <c r="T8" t="n">
+        <v>21455.9617009573</v>
+      </c>
+      <c r="U8" t="n">
+        <v>33524.82508097305</v>
+      </c>
+      <c r="V8" t="n">
+        <v>34995.67803892875</v>
+      </c>
+      <c r="W8" t="n">
+        <v>31255.16922470855</v>
+      </c>
+      <c r="X8" t="n">
+        <v>37428.3767000022</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>39103.0583392229</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>39641.05297196111</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>30999.12904895455</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>37375.6958246628</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>38463.622489347</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>34623.35397996476</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>21454.49190460345</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>27907.9610106319</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>18169.5295278442</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>28360.37000808385</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>27654.3799284192</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>31482.892069442</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>37549.47926332404</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>33928.98227626435</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>32445.7307693277</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>29680.74692954965</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>30494.5329977343</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>22467.2991333637</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>27684.01901972245</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>24771.36400683615</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>40609.48305534615</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>35016.09468676989</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>34872.7198678155</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>58938.8195</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>47926.83632931147</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>49879.80816358644</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>47102.71896187135</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>43830.33723661795</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>97900.5914541083</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>62239.53125919632</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>99410.86126558283</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>51836.51446690785</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>59163.12972596447</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>57568.7952600243</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>62052.53102559906</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>61265.22755491319</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>66740</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>33667.77899637665</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>44654.505</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>42865</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>37320.75</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>48212</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>49682.72769359915</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>31746.90135544375</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>66046.29449421521</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>66704.75722169633</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>79159.61374579441</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>85452.05509517266</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>64971.29226966516</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>76318.50865996671</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>79502.08765670167</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>77635.48292601698</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>67920.31197821039</v>
       </c>
     </row>
     <row r="9">
@@ -798,40 +2462,232 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2827568.866170935</v>
+        <v>8122726.592434363</v>
       </c>
       <c r="C9" t="n">
-        <v>3441293.778590984</v>
+        <v>3086139.294757853</v>
       </c>
       <c r="D9" t="n">
-        <v>2997519.452074238</v>
+        <v>7204266.742329176</v>
       </c>
       <c r="E9" t="n">
-        <v>3474572.365462308</v>
+        <v>2569139.925782104</v>
       </c>
       <c r="F9" t="n">
-        <v>3766905.59001234</v>
+        <v>1698316.65470918</v>
       </c>
       <c r="G9" t="n">
-        <v>2753403.630072502</v>
+        <v>1466816.39147648</v>
       </c>
       <c r="H9" t="n">
-        <v>2173211.290130805</v>
+        <v>1924986.18972528</v>
       </c>
       <c r="I9" t="n">
-        <v>3039979.376189653</v>
+        <v>2693794.69019408</v>
       </c>
       <c r="J9" t="n">
-        <v>6004868.809911354</v>
+        <v>3265940.9522993</v>
       </c>
       <c r="K9" t="n">
-        <v>2247437.265527637</v>
+        <v>2398317.22903388</v>
       </c>
       <c r="L9" t="n">
-        <v>5375654.536827597</v>
+        <v>1673813.56260536</v>
       </c>
       <c r="M9" t="n">
-        <v>4239740.357313359</v>
+        <v>1671361.1306579</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1447457.46153008</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1953657.1430926</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2014199.06168294</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1790822.73193406</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1443755.52817518</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1564591.58663698</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1970313.74127984</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2470661.90715718</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2527283.75416462</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2105847.42581576</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2421202.90838998</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2861788.170666261</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2785112.37681754</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5038810.982452061</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>5636538.305159081</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>6049808.34863592</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3456150.8082959</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1599383.84789106</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2408499.85809554</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1153911.62847246</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1847383.16277328</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1963689.22389178</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2583918.8280532</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>3856207.218654341</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2799825.38531674</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>3081100.34485264</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2326375.29938</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1977546.07586316</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2151719.3254238</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3293436.0035962</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1824004.88094594</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2287799.90739608</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3008709.25558984</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2736623.22405714</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2040565.936933333</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2650588.786217585</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2980879.128088631</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>5498558.33502333</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5568349.405127079</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3672230.851263796</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2530817.22048714</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3841111.080042755</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2055972.214523255</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2325577.519082672</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2181179.000166196</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2348400.968177486</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2267621.734259108</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1643440</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1589836.91145789</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1575311</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1276423</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>816687</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1270793</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1392598.80028636</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>746357.568074079</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>3989325.64061538</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>3563066.28214841</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>2186908.808510384</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1526611.414481163</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1197000.573967651</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1459414.066163923</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1515763.911566187</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1527797.363900427</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1382972.910274663</v>
       </c>
     </row>
   </sheetData>

--- a/data/proteomics/protein_copy_statistical_top1000.xlsx
+++ b/data/proteomics/protein_copy_statistical_top1000.xlsx
@@ -456,207 +456,207 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>prot.10</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>prot.11</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>prot.12</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>prot.13</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>prot.14</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>prot.15</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>prot.16</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>prot.17</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>prot.18</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>prot.19</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>prot.2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>prot.20</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>prot.21</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>prot.22</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>prot.23</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>prot.24</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>prot.25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>prot.26</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>prot.27</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>prot.28</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>prot.29</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>prot.3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>prot.30</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>prot.31</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>prot.32</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>prot.33</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>prot.34</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>prot.35</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>prot.36</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>prot.37</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>prot.38</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>prot.39</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>prot.4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>prot.40</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>prot.41</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>prot.42</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>prot.5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>prot.6</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>prot.7</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>prot.8</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>prot.9</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>prot.10</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>prot.11</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>prot.12</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prot.13</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>prot.14</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>prot.15</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>prot.16</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>prot.17</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>prot.18</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>prot.19</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>prot.20</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>prot.21</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>prot.22</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>prot.23</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>prot.24</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>prot.25</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>prot.26</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>prot.27</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>prot.28</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>prot.29</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>prot.30</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>prot.31</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>prot.32</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>prot.33</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>prot.34</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>prot.35</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>prot.36</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>prot.37</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>prot.38</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>prot.39</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>prot.40</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>prot.41</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>prot.42</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
@@ -1064,130 +1064,130 @@
         <v>105064.9080032164</v>
       </c>
       <c r="F3" t="n">
-        <v>38526.59640408488</v>
+        <v>38525.24155144845</v>
       </c>
       <c r="G3" t="n">
-        <v>34693.48548003553</v>
+        <v>43290.55543928633</v>
       </c>
       <c r="H3" t="n">
-        <v>37168.14778022456</v>
+        <v>37038.66398542648</v>
       </c>
       <c r="I3" t="n">
-        <v>55166.83707125369</v>
+        <v>37049.69751370615</v>
       </c>
       <c r="J3" t="n">
-        <v>58873.38541922928</v>
+        <v>40837.33308003151</v>
       </c>
       <c r="K3" t="n">
-        <v>49578.10471780638</v>
+        <v>39847.60282598255</v>
       </c>
       <c r="L3" t="n">
-        <v>28609.71781178535</v>
+        <v>40191.2456289303</v>
       </c>
       <c r="M3" t="n">
-        <v>30222.15759491802</v>
+        <v>68185.90319859645</v>
       </c>
       <c r="N3" t="n">
-        <v>39960.17206208715</v>
+        <v>68300.36551275357</v>
       </c>
       <c r="O3" t="n">
-        <v>43292.15446450197</v>
+        <v>64551.27514691396</v>
       </c>
       <c r="P3" t="n">
-        <v>37040.0009527303</v>
+        <v>84920.98671372708</v>
       </c>
       <c r="Q3" t="n">
-        <v>37051.09863199265</v>
+        <v>34692.25925999735</v>
       </c>
       <c r="R3" t="n">
-        <v>40838.82650441667</v>
+        <v>89688.82595623491</v>
       </c>
       <c r="S3" t="n">
-        <v>39849.08103696295</v>
+        <v>89382.30386128626</v>
       </c>
       <c r="T3" t="n">
-        <v>40192.75463917518</v>
+        <v>76680.59009819463</v>
       </c>
       <c r="U3" t="n">
-        <v>68188.02035978963</v>
+        <v>92755.48688594722</v>
       </c>
       <c r="V3" t="n">
-        <v>68302.52225944481</v>
+        <v>95245.92494849784</v>
       </c>
       <c r="W3" t="n">
-        <v>64553.2746363598</v>
+        <v>73108.65300605455</v>
       </c>
       <c r="X3" t="n">
-        <v>84923.25512229696</v>
+        <v>43121.54018601456</v>
       </c>
       <c r="Y3" t="n">
-        <v>89691.19445015976</v>
+        <v>53696.50110002611</v>
       </c>
       <c r="Z3" t="n">
-        <v>89384.77250020954</v>
+        <v>30859.44335696471</v>
       </c>
       <c r="AA3" t="n">
-        <v>76682.69396234934</v>
+        <v>50471.21048951334</v>
       </c>
       <c r="AB3" t="n">
-        <v>92758.04731701875</v>
+        <v>37166.90523415687</v>
       </c>
       <c r="AC3" t="n">
-        <v>95248.41993361684</v>
+        <v>50108.08483965501</v>
       </c>
       <c r="AD3" t="n">
-        <v>73110.99248757317</v>
+        <v>58123.26071996987</v>
       </c>
       <c r="AE3" t="n">
-        <v>43122.94808525473</v>
+        <v>72325.18520311838</v>
       </c>
       <c r="AF3" t="n">
-        <v>53698.23620652136</v>
+        <v>62102.80501737414</v>
       </c>
       <c r="AG3" t="n">
-        <v>30860.52910408555</v>
+        <v>58411.01551273657</v>
       </c>
       <c r="AH3" t="n">
-        <v>50473.06163056983</v>
+        <v>52606.25504036327</v>
       </c>
       <c r="AI3" t="n">
-        <v>50109.96282314113</v>
+        <v>55480.42469234934</v>
       </c>
       <c r="AJ3" t="n">
-        <v>58125.27215142745</v>
+        <v>46104.68765870777</v>
       </c>
       <c r="AK3" t="n">
-        <v>72327.59058242066</v>
+        <v>60212.98484765529</v>
       </c>
       <c r="AL3" t="n">
-        <v>62104.85691750222</v>
+        <v>51407.68744604568</v>
       </c>
       <c r="AM3" t="n">
-        <v>58413.23388771783</v>
+        <v>55165.18960193404</v>
       </c>
       <c r="AN3" t="n">
-        <v>52608.21437278811</v>
+        <v>70176.11324328372</v>
       </c>
       <c r="AO3" t="n">
-        <v>55482.51196158198</v>
+        <v>67279.84453204843</v>
       </c>
       <c r="AP3" t="n">
-        <v>46106.19990032677</v>
+        <v>65418.92873185271</v>
       </c>
       <c r="AQ3" t="n">
-        <v>60214.95839389114</v>
+        <v>58871.63098931144</v>
       </c>
       <c r="AR3" t="n">
-        <v>51409.28057582907</v>
+        <v>49576.59235267542</v>
       </c>
       <c r="AS3" t="n">
-        <v>70178.35267045889</v>
+        <v>28608.64498512408</v>
       </c>
       <c r="AT3" t="n">
-        <v>67282.09186947322</v>
+        <v>30221.03330162288</v>
       </c>
       <c r="AU3" t="n">
-        <v>65420.9956137284</v>
+        <v>39958.96152187726</v>
       </c>
       <c r="AV3" t="n">
         <v>56218.47606892</v>
@@ -1208,7 +1208,7 @@
         <v>120801.1173720551</v>
       </c>
       <c r="BB3" t="n">
-        <v>76215.01799274821</v>
+        <v>76215.01799274819</v>
       </c>
       <c r="BC3" t="n">
         <v>122161.0464563577</v>
@@ -1235,7 +1235,7 @@
         <v>41362.54604555698</v>
       </c>
       <c r="BK3" t="n">
-        <v>50762.72378199999</v>
+        <v>50762.72378200001</v>
       </c>
       <c r="BL3" t="n">
         <v>60220.1</v>
@@ -1253,31 +1253,31 @@
         <v>30790.68569767767</v>
       </c>
       <c r="BQ3" t="n">
-        <v>70924.98469309551</v>
+        <v>70889.25733338314</v>
       </c>
       <c r="BR3" t="n">
-        <v>72950.20005716999</v>
+        <v>72913.62491444954</v>
       </c>
       <c r="BS3" t="n">
-        <v>79867.75266700536</v>
+        <v>79823.08297607297</v>
       </c>
       <c r="BT3" t="n">
-        <v>87516.54554463542</v>
+        <v>87467.61277985698</v>
       </c>
       <c r="BU3" t="n">
-        <v>64794.27683459198</v>
+        <v>64757.12483680325</v>
       </c>
       <c r="BV3" t="n">
-        <v>75137.10070382197</v>
+        <v>75096.59740076191</v>
       </c>
       <c r="BW3" t="n">
-        <v>77434.88225229445</v>
+        <v>77394.39151096725</v>
       </c>
       <c r="BX3" t="n">
-        <v>80408.53506490917</v>
+        <v>80368.24318090208</v>
       </c>
       <c r="BY3" t="n">
-        <v>72536.49882266636</v>
+        <v>72500.79236117276</v>
       </c>
     </row>
     <row r="4">
@@ -1299,136 +1299,136 @@
         <v>265290.3972004985</v>
       </c>
       <c r="F4" t="n">
-        <v>114124.8546349758</v>
+        <v>114112.5414985815</v>
       </c>
       <c r="G4" t="n">
-        <v>103241.2458695453</v>
+        <v>121817.5456611645</v>
       </c>
       <c r="H4" t="n">
-        <v>116074.2745859909</v>
+        <v>108892.3008986797</v>
       </c>
       <c r="I4" t="n">
-        <v>194741.9629844958</v>
+        <v>105909.5325135366</v>
       </c>
       <c r="J4" t="n">
-        <v>213849.7020006684</v>
+        <v>111484.5478750699</v>
       </c>
       <c r="K4" t="n">
-        <v>165591.2353694275</v>
+        <v>109472.2600882738</v>
       </c>
       <c r="L4" t="n">
-        <v>88033.84215074276</v>
+        <v>116244.5194148154</v>
       </c>
       <c r="M4" t="n">
-        <v>91808.1369340705</v>
+        <v>199115.7612302144</v>
       </c>
       <c r="N4" t="n">
-        <v>116068.9523166056</v>
+        <v>193992.6713055037</v>
       </c>
       <c r="O4" t="n">
-        <v>121835.6145666198</v>
+        <v>181501.482790138</v>
       </c>
       <c r="P4" t="n">
-        <v>108909.6174784841</v>
+        <v>242564.5071480609</v>
       </c>
       <c r="Q4" t="n">
-        <v>105925.601315764</v>
+        <v>103231.6224955287</v>
       </c>
       <c r="R4" t="n">
-        <v>111501.1654192605</v>
+        <v>261507.2549050615</v>
       </c>
       <c r="S4" t="n">
-        <v>109493.907562838</v>
+        <v>254231.5917755708</v>
       </c>
       <c r="T4" t="n">
-        <v>116261.8476219478</v>
+        <v>304058.1259623535</v>
       </c>
       <c r="U4" t="n">
-        <v>199141.7879318864</v>
+        <v>358407.8120985716</v>
       </c>
       <c r="V4" t="n">
-        <v>194023.0141419295</v>
+        <v>358859.9940626418</v>
       </c>
       <c r="W4" t="n">
-        <v>181534.6670459086</v>
+        <v>229529.7032113277</v>
       </c>
       <c r="X4" t="n">
-        <v>242606.7664132215</v>
+        <v>128178.4775853196</v>
       </c>
       <c r="Y4" t="n">
-        <v>261549.1295274351</v>
+        <v>164250.7310014596</v>
       </c>
       <c r="Z4" t="n">
-        <v>254268.5662500033</v>
+        <v>84454.53893166859</v>
       </c>
       <c r="AA4" t="n">
-        <v>304067.2123832731</v>
+        <v>137509.1225537218</v>
       </c>
       <c r="AB4" t="n">
-        <v>358420.0042492593</v>
+        <v>116059.4480006163</v>
       </c>
       <c r="AC4" t="n">
-        <v>358873.2615219346</v>
+        <v>136433.9649562255</v>
       </c>
       <c r="AD4" t="n">
-        <v>229548.699067146</v>
+        <v>176010.7806602259</v>
       </c>
       <c r="AE4" t="n">
-        <v>128192.2549721611</v>
+        <v>232357.9356134105</v>
       </c>
       <c r="AF4" t="n">
-        <v>164266.3687433067</v>
+        <v>186995.9810682866</v>
       </c>
       <c r="AG4" t="n">
-        <v>84467.52871055336</v>
+        <v>171548.1527937211</v>
       </c>
       <c r="AH4" t="n">
-        <v>137526.5194625088</v>
+        <v>146742.1151553687</v>
       </c>
       <c r="AI4" t="n">
-        <v>136453.6267988162</v>
+        <v>151594.3971739073</v>
       </c>
       <c r="AJ4" t="n">
-        <v>176027.7988613566</v>
+        <v>140473.1800386804</v>
       </c>
       <c r="AK4" t="n">
-        <v>232378.0488984839</v>
+        <v>193938.2604777707</v>
       </c>
       <c r="AL4" t="n">
-        <v>187014.9221617106</v>
+        <v>154311.1855863388</v>
       </c>
       <c r="AM4" t="n">
-        <v>171566.6002991211</v>
+        <v>194725.6325791561</v>
       </c>
       <c r="AN4" t="n">
-        <v>146758.7569109736</v>
+        <v>201981.4260514785</v>
       </c>
       <c r="AO4" t="n">
-        <v>151615.8301893591</v>
+        <v>199329.6971674449</v>
       </c>
       <c r="AP4" t="n">
-        <v>140484.4375324663</v>
+        <v>192611.4489821127</v>
       </c>
       <c r="AQ4" t="n">
-        <v>193950.9127080156</v>
+        <v>213835.9100481668</v>
       </c>
       <c r="AR4" t="n">
-        <v>154324.4473354669</v>
+        <v>165578.8521856312</v>
       </c>
       <c r="AS4" t="n">
-        <v>202006.3943943077</v>
+        <v>88022.48117669713</v>
       </c>
       <c r="AT4" t="n">
-        <v>199344.6501770437</v>
+        <v>91797.20238559357</v>
       </c>
       <c r="AU4" t="n">
-        <v>192631.4129956177</v>
+        <v>116043.5728094426</v>
       </c>
       <c r="AV4" t="n">
         <v>116774.1687569073</v>
       </c>
       <c r="AW4" t="n">
-        <v>323028.6516446972</v>
+        <v>323028.6516446971</v>
       </c>
       <c r="AX4" t="n">
         <v>341876.5071832517</v>
@@ -1452,7 +1452,7 @@
         <v>147978.1554881051</v>
       </c>
       <c r="BE4" t="n">
-        <v>198920.2825271325</v>
+        <v>198920.2825271324</v>
       </c>
       <c r="BF4" t="n">
         <v>194530.08111154</v>
@@ -1470,7 +1470,7 @@
         <v>104347.9899609492</v>
       </c>
       <c r="BK4" t="n">
-        <v>98800.74813665492</v>
+        <v>98800.74813665493</v>
       </c>
       <c r="BL4" t="n">
         <v>132525.3106954099</v>
@@ -1485,34 +1485,34 @@
         <v>105254.0294787811</v>
       </c>
       <c r="BP4" t="n">
-        <v>58464.14349249626</v>
+        <v>58464.14349249625</v>
       </c>
       <c r="BQ4" t="n">
-        <v>185457.1202674733</v>
+        <v>183630.6761575444</v>
       </c>
       <c r="BR4" t="n">
-        <v>176927.7799525312</v>
+        <v>175044.1043340405</v>
       </c>
       <c r="BS4" t="n">
-        <v>149536.3129686545</v>
+        <v>146071.80647298</v>
       </c>
       <c r="BT4" t="n">
-        <v>148794.6844269141</v>
+        <v>144246.5465888265</v>
       </c>
       <c r="BU4" t="n">
-        <v>104494.6003619383</v>
+        <v>100513.7070756429</v>
       </c>
       <c r="BV4" t="n">
-        <v>122672.8504187998</v>
+        <v>117667.0199494147</v>
       </c>
       <c r="BW4" t="n">
-        <v>124397.3728050634</v>
+        <v>119128.8110233855</v>
       </c>
       <c r="BX4" t="n">
-        <v>131096.9176983922</v>
+        <v>125926.097834186</v>
       </c>
       <c r="BY4" t="n">
-        <v>120663.2753959248</v>
+        <v>116054.7014620051</v>
       </c>
     </row>
     <row r="5">
@@ -1534,130 +1534,130 @@
         <v>5366.744646409529</v>
       </c>
       <c r="F5" t="n">
-        <v>1354.85263643356</v>
+        <v>1359.25498767938</v>
       </c>
       <c r="G5" t="n">
-        <v>1226.22003817918</v>
+        <v>1600.0832314654</v>
       </c>
       <c r="H5" t="n">
-        <v>1242.54606769128</v>
+        <v>1337.88395729494</v>
       </c>
       <c r="I5" t="n">
-        <v>1647.46931965286</v>
+        <v>1405.66328496198</v>
       </c>
       <c r="J5" t="n">
-        <v>1754.4299178406</v>
+        <v>1494.73947601594</v>
       </c>
       <c r="K5" t="n">
-        <v>1512.36513096614</v>
+        <v>1489.13362500364</v>
       </c>
       <c r="L5" t="n">
-        <v>1072.82666127318</v>
+        <v>1509.1074463696</v>
       </c>
       <c r="M5" t="n">
-        <v>1124.29329514348</v>
+        <v>2126.61689579812</v>
       </c>
       <c r="N5" t="n">
-        <v>1210.54020989088</v>
+        <v>2162.041501095961</v>
       </c>
       <c r="O5" t="n">
-        <v>1599.02521564676</v>
+        <v>2000.14977828292</v>
       </c>
       <c r="P5" t="n">
-        <v>1336.96730381742</v>
+        <v>2276.46511465164</v>
       </c>
       <c r="Q5" t="n">
-        <v>1401.11828650486</v>
+        <v>1226.7300627384</v>
       </c>
       <c r="R5" t="n">
-        <v>1493.42438515688</v>
+        <v>2385.72528595038</v>
       </c>
       <c r="S5" t="n">
-        <v>1478.21098040352</v>
+        <v>2474.59840409452</v>
       </c>
       <c r="T5" t="n">
-        <v>1509.01024488346</v>
+        <v>2104.44524878918</v>
       </c>
       <c r="U5" t="n">
-        <v>2117.16119319826</v>
+        <v>2561.9020568372</v>
       </c>
       <c r="V5" t="n">
-        <v>2156.7466912376</v>
+        <v>2501.99007619308</v>
       </c>
       <c r="W5" t="n">
-        <v>1999.48944583608</v>
+        <v>2340.4220153886</v>
       </c>
       <c r="X5" t="n">
-        <v>2268.40856990748</v>
+        <v>1409.92334212048</v>
       </c>
       <c r="Y5" t="n">
-        <v>2368.49392485156</v>
+        <v>1738.03316409404</v>
       </c>
       <c r="Z5" t="n">
-        <v>2468.63892329714</v>
+        <v>1091.92548134868</v>
       </c>
       <c r="AA5" t="n">
-        <v>2103.86415470132</v>
+        <v>1851.89239157208</v>
       </c>
       <c r="AB5" t="n">
-        <v>2560.43107152822</v>
+        <v>1246.3122320275</v>
       </c>
       <c r="AC5" t="n">
-        <v>2494.98511900176</v>
+        <v>1891.93994176902</v>
       </c>
       <c r="AD5" t="n">
-        <v>2339.48151860412</v>
+        <v>2011.7999029117</v>
       </c>
       <c r="AE5" t="n">
-        <v>1407.899240165</v>
+        <v>2415.82215316596</v>
       </c>
       <c r="AF5" t="n">
-        <v>1735.10649525422</v>
+        <v>2052.63830127466</v>
       </c>
       <c r="AG5" t="n">
-        <v>1085.74712084124</v>
+        <v>2222.69414402002</v>
       </c>
       <c r="AH5" t="n">
-        <v>1851.14105649176</v>
+        <v>1973.84876600516</v>
       </c>
       <c r="AI5" t="n">
-        <v>1877.98348612886</v>
+        <v>2091.56599119468</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2011.43145757906</v>
+        <v>1514.67558593318</v>
       </c>
       <c r="AK5" t="n">
-        <v>2405.37930226726</v>
+        <v>1985.21760193702</v>
       </c>
       <c r="AL5" t="n">
-        <v>2051.90012808814</v>
+        <v>1593.46558394386</v>
       </c>
       <c r="AM5" t="n">
-        <v>2218.37498126728</v>
+        <v>1648.98713734458</v>
       </c>
       <c r="AN5" t="n">
-        <v>1959.3324248564</v>
+        <v>2244.37839694068</v>
       </c>
       <c r="AO5" t="n">
-        <v>2087.26923263166</v>
+        <v>2254.43683832752</v>
       </c>
       <c r="AP5" t="n">
-        <v>1512.24161900306</v>
+        <v>2066.92516273012</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1973.54623584382</v>
+        <v>1760.02604189236</v>
       </c>
       <c r="AR5" t="n">
-        <v>1593.12978339636</v>
+        <v>1519.21504245786</v>
       </c>
       <c r="AS5" t="n">
-        <v>2239.4271751489</v>
+        <v>1076.95905354268</v>
       </c>
       <c r="AT5" t="n">
-        <v>2247.33742477794</v>
+        <v>1127.19433391598</v>
       </c>
       <c r="AU5" t="n">
-        <v>2066.88187568082</v>
+        <v>1213.87284368196</v>
       </c>
       <c r="AV5" t="n">
         <v>4165.453600000001</v>
@@ -1723,31 +1723,31 @@
         <v>7300.91952348227</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7090.977841208077</v>
+        <v>7171.871440400177</v>
       </c>
       <c r="BR5" t="n">
-        <v>7295.643844303476</v>
+        <v>7346.571580202123</v>
       </c>
       <c r="BS5" t="n">
-        <v>8870.156847249267</v>
+        <v>9005.691306435867</v>
       </c>
       <c r="BT5" t="n">
-        <v>9727.164099679872</v>
+        <v>9839.459091145916</v>
       </c>
       <c r="BU5" t="n">
-        <v>7407.232072230986</v>
+        <v>7475.505364055657</v>
       </c>
       <c r="BV5" t="n">
-        <v>8059.196314854126</v>
+        <v>8156.726880743076</v>
       </c>
       <c r="BW5" t="n">
-        <v>8058.01094541416</v>
+        <v>8184.260976247137</v>
       </c>
       <c r="BX5" t="n">
-        <v>8031.876061071963</v>
+        <v>8096.554037333866</v>
       </c>
       <c r="BY5" t="n">
-        <v>7106.518614424131</v>
+        <v>7164.26178754857</v>
       </c>
     </row>
     <row r="6">
@@ -1769,130 +1769,130 @@
         <v>8825.138567073458</v>
       </c>
       <c r="F6" t="n">
-        <v>2544.255144175745</v>
+        <v>2546.15399105892</v>
       </c>
       <c r="G6" t="n">
-        <v>2338.559765773605</v>
+        <v>3068.051905441875</v>
       </c>
       <c r="H6" t="n">
-        <v>2437.673375984386</v>
+        <v>2598.607777338705</v>
       </c>
       <c r="I6" t="n">
-        <v>3225.853971425305</v>
+        <v>2654.280956773875</v>
       </c>
       <c r="J6" t="n">
-        <v>3471.32282981583</v>
+        <v>2882.75889704484</v>
       </c>
       <c r="K6" t="n">
-        <v>2998.3552588275</v>
+        <v>2804.52838600594</v>
       </c>
       <c r="L6" t="n">
-        <v>2019.981178131566</v>
+        <v>2852.39001631342</v>
       </c>
       <c r="M6" t="n">
-        <v>2153.63301545458</v>
+        <v>4004.12834834034</v>
       </c>
       <c r="N6" t="n">
-        <v>2379.8967468133</v>
+        <v>4001.787466183265</v>
       </c>
       <c r="O6" t="n">
-        <v>3065.38373333841</v>
+        <v>3687.44296444887</v>
       </c>
       <c r="P6" t="n">
-        <v>2580.319726789365</v>
+        <v>4430.201668836736</v>
       </c>
       <c r="Q6" t="n">
-        <v>2647.60000512359</v>
+        <v>2341.6938567814</v>
       </c>
       <c r="R6" t="n">
-        <v>2879.78136112634</v>
+        <v>4462.24245831111</v>
       </c>
       <c r="S6" t="n">
-        <v>2800.24721540025</v>
+        <v>4543.475517760355</v>
       </c>
       <c r="T6" t="n">
-        <v>2848.23995218532</v>
+        <v>4138.409941566724</v>
       </c>
       <c r="U6" t="n">
-        <v>4000.688118024895</v>
+        <v>4831.410853993844</v>
       </c>
       <c r="V6" t="n">
-        <v>3995.70819042461</v>
+        <v>5024.52610154451</v>
       </c>
       <c r="W6" t="n">
-        <v>3681.603186221125</v>
+        <v>4574.07653503196</v>
       </c>
       <c r="X6" t="n">
-        <v>4425.33979935234</v>
+        <v>2732.156010943865</v>
       </c>
       <c r="Y6" t="n">
-        <v>4460.887174152475</v>
+        <v>3483.546787763185</v>
       </c>
       <c r="Z6" t="n">
-        <v>4529.85789260455</v>
+        <v>2129.106052835245</v>
       </c>
       <c r="AA6" t="n">
-        <v>4132.282241039755</v>
+        <v>3556.424372644715</v>
       </c>
       <c r="AB6" t="n">
-        <v>4817.43531536938</v>
+        <v>2443.10786849602</v>
       </c>
       <c r="AC6" t="n">
-        <v>5016.26149826538</v>
+        <v>3614.64336907322</v>
       </c>
       <c r="AD6" t="n">
-        <v>4563.5995094052</v>
+        <v>3925.37963255867</v>
       </c>
       <c r="AE6" t="n">
-        <v>2729.88574888491</v>
+        <v>4638.843987039405</v>
       </c>
       <c r="AF6" t="n">
-        <v>3478.5146784608</v>
+        <v>4095.57302061765</v>
       </c>
       <c r="AG6" t="n">
-        <v>2125.095596390085</v>
+        <v>4192.40398378758</v>
       </c>
       <c r="AH6" t="n">
-        <v>3553.65047436036</v>
+        <v>3835.597061416836</v>
       </c>
       <c r="AI6" t="n">
-        <v>3605.545815814746</v>
+        <v>3948.752549994286</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3922.537465856625</v>
+        <v>2982.40827423979</v>
       </c>
       <c r="AK6" t="n">
-        <v>4631.824013074665</v>
+        <v>3788.826444837115</v>
       </c>
       <c r="AL6" t="n">
-        <v>4086.54599252097</v>
+        <v>3237.347480479586</v>
       </c>
       <c r="AM6" t="n">
-        <v>4188.61961438338</v>
+        <v>3228.055746810895</v>
       </c>
       <c r="AN6" t="n">
-        <v>3831.02181233167</v>
+        <v>4506.990911789576</v>
       </c>
       <c r="AO6" t="n">
-        <v>3938.190293079625</v>
+        <v>4420.896110090185</v>
       </c>
       <c r="AP6" t="n">
-        <v>2980.824811700615</v>
+        <v>4270.211394749411</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3787.67072074853</v>
+        <v>3473.496127631585</v>
       </c>
       <c r="AR6" t="n">
-        <v>3225.514541765505</v>
+        <v>3025.30316487487</v>
       </c>
       <c r="AS6" t="n">
-        <v>4502.004219242091</v>
+        <v>2028.03172740212</v>
       </c>
       <c r="AT6" t="n">
-        <v>4418.12505754664</v>
+        <v>2159.8655237269</v>
       </c>
       <c r="AU6" t="n">
-        <v>4232.98804714863</v>
+        <v>2381.42152558871</v>
       </c>
       <c r="AV6" t="n">
         <v>10983.90443333333</v>
@@ -1958,31 +1958,31 @@
         <v>9911.003395444628</v>
       </c>
       <c r="BQ6" t="n">
-        <v>13046.67396565851</v>
+        <v>13145.02653676005</v>
       </c>
       <c r="BR6" t="n">
-        <v>13249.19716256196</v>
+        <v>13315.78471393977</v>
       </c>
       <c r="BS6" t="n">
-        <v>15739.09937999126</v>
+        <v>15975.1427936593</v>
       </c>
       <c r="BT6" t="n">
-        <v>17157.53058715043</v>
+        <v>17379.99491511496</v>
       </c>
       <c r="BU6" t="n">
-        <v>12671.56603839952</v>
+        <v>12806.48669811124</v>
       </c>
       <c r="BV6" t="n">
-        <v>13669.8226236754</v>
+        <v>13831.87449951545</v>
       </c>
       <c r="BW6" t="n">
-        <v>13586.43830529653</v>
+        <v>13857.31945828538</v>
       </c>
       <c r="BX6" t="n">
-        <v>13635.31195705756</v>
+        <v>13731.29031274336</v>
       </c>
       <c r="BY6" t="n">
-        <v>12215.30587910782</v>
+        <v>12290.72621400194</v>
       </c>
     </row>
     <row r="7">
@@ -2004,130 +2004,130 @@
         <v>17401.07496193696</v>
       </c>
       <c r="F7" t="n">
-        <v>6420.7192586746</v>
+        <v>6433.183825005741</v>
       </c>
       <c r="G7" t="n">
-        <v>5737.126536054981</v>
+        <v>7015.78040724737</v>
       </c>
       <c r="H7" t="n">
-        <v>5994.483038210481</v>
+        <v>5870.717753696181</v>
       </c>
       <c r="I7" t="n">
-        <v>7906.828973420301</v>
+        <v>6147.065370372851</v>
       </c>
       <c r="J7" t="n">
-        <v>7902.751264474</v>
+        <v>6476.540743917531</v>
       </c>
       <c r="K7" t="n">
-        <v>6732.8812484846</v>
+        <v>6214.62994620039</v>
       </c>
       <c r="L7" t="n">
-        <v>4620.152265865951</v>
+        <v>6456.6186215465</v>
       </c>
       <c r="M7" t="n">
-        <v>4914.705515834179</v>
+        <v>9074.628919481398</v>
       </c>
       <c r="N7" t="n">
-        <v>5723.4884095466</v>
+        <v>9238.326657698601</v>
       </c>
       <c r="O7" t="n">
-        <v>6990.654033310311</v>
+        <v>8522.558075878</v>
       </c>
       <c r="P7" t="n">
-        <v>5860.481511253491</v>
+        <v>9964.214570911699</v>
       </c>
       <c r="Q7" t="n">
-        <v>6143.514517706831</v>
+        <v>5762.434388313461</v>
       </c>
       <c r="R7" t="n">
-        <v>6433.232892404891</v>
+        <v>10303.9120137866</v>
       </c>
       <c r="S7" t="n">
-        <v>6173.20062578461</v>
+        <v>10955.7337303249</v>
       </c>
       <c r="T7" t="n">
-        <v>6443.91032254563</v>
+        <v>9335.4570101056</v>
       </c>
       <c r="U7" t="n">
-        <v>9063.086893854401</v>
+        <v>11396.3320206054</v>
       </c>
       <c r="V7" t="n">
-        <v>9218.0607158904</v>
+        <v>11664.0997843315</v>
       </c>
       <c r="W7" t="n">
-        <v>8505.339053760999</v>
+        <v>10167.358172081</v>
       </c>
       <c r="X7" t="n">
-        <v>9920.5704200933</v>
+        <v>6231.530254350941</v>
       </c>
       <c r="Y7" t="n">
-        <v>10229.4795468976</v>
+        <v>7706.623817501511</v>
       </c>
       <c r="Z7" t="n">
-        <v>10933.2732874068</v>
+        <v>4771.44908384727</v>
       </c>
       <c r="AA7" t="n">
-        <v>9295.9143551659</v>
+        <v>8084.3820634192</v>
       </c>
       <c r="AB7" t="n">
-        <v>11337.8507863621</v>
+        <v>6007.061201237471</v>
       </c>
       <c r="AC7" t="n">
-        <v>11560.1850707354</v>
+        <v>8390.5512926499</v>
       </c>
       <c r="AD7" t="n">
-        <v>10127.1748006924</v>
+        <v>8702.053794065501</v>
       </c>
       <c r="AE7" t="n">
-        <v>6223.31277002523</v>
+        <v>10443.1617378451</v>
       </c>
       <c r="AF7" t="n">
-        <v>7690.083883725761</v>
+        <v>9494.667979305301</v>
       </c>
       <c r="AG7" t="n">
-        <v>4763.82346389081</v>
+        <v>9449.625265695999</v>
       </c>
       <c r="AH7" t="n">
-        <v>8050.60466639</v>
+        <v>8517.997424867699</v>
       </c>
       <c r="AI7" t="n">
-        <v>8334.779447164499</v>
+        <v>8953.759173305101</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8610.890567472601</v>
+        <v>6672.179374518571</v>
       </c>
       <c r="AK7" t="n">
-        <v>10410.6485873027</v>
+        <v>8260.8877062635</v>
       </c>
       <c r="AL7" t="n">
-        <v>9461.3718331033</v>
+        <v>7221.08691745804</v>
       </c>
       <c r="AM7" t="n">
-        <v>9378.8632367914</v>
+        <v>7910.137752942701</v>
       </c>
       <c r="AN7" t="n">
-        <v>8503.7749141895</v>
+        <v>10260.7735740906</v>
       </c>
       <c r="AO7" t="n">
-        <v>8939.7311000503</v>
+        <v>10057.3663513851</v>
       </c>
       <c r="AP7" t="n">
-        <v>6640.853450677821</v>
+        <v>9592.8995813376</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8225.940231752098</v>
+        <v>7945.3851636027</v>
       </c>
       <c r="AR7" t="n">
-        <v>7216.70717006184</v>
+        <v>6739.87264876871</v>
       </c>
       <c r="AS7" t="n">
-        <v>10226.2691096632</v>
+        <v>4665.676151221471</v>
       </c>
       <c r="AT7" t="n">
-        <v>10042.5063109866</v>
+        <v>4925.5940107616</v>
       </c>
       <c r="AU7" t="n">
-        <v>9575.0604508053</v>
+        <v>5741.803564123111</v>
       </c>
       <c r="AV7" t="n">
         <v>26190.681</v>
@@ -2193,31 +2193,31 @@
         <v>15366.954286114</v>
       </c>
       <c r="BQ7" t="n">
-        <v>25726.6702483996</v>
+        <v>26072.75352271854</v>
       </c>
       <c r="BR7" t="n">
-        <v>26714.12558138224</v>
+        <v>27285.0469777728</v>
       </c>
       <c r="BS7" t="n">
-        <v>30963.38759736533</v>
+        <v>31315.39524706842</v>
       </c>
       <c r="BT7" t="n">
-        <v>32869.87611887697</v>
+        <v>33227.54828506184</v>
       </c>
       <c r="BU7" t="n">
-        <v>24488.04282112215</v>
+        <v>24566.68516756937</v>
       </c>
       <c r="BV7" t="n">
-        <v>26808.61193964766</v>
+        <v>27145.58539021827</v>
       </c>
       <c r="BW7" t="n">
-        <v>27600.8202719678</v>
+        <v>27687.49253304677</v>
       </c>
       <c r="BX7" t="n">
-        <v>27110.01043305021</v>
+        <v>27391.84579989535</v>
       </c>
       <c r="BY7" t="n">
-        <v>24344.8954868173</v>
+        <v>24551.53926768807</v>
       </c>
     </row>
     <row r="8">
@@ -2239,130 +2239,130 @@
         <v>52033.9561581314</v>
       </c>
       <c r="F8" t="n">
-        <v>19652.3192507939</v>
+        <v>20026.11370509145</v>
       </c>
       <c r="G8" t="n">
-        <v>17467.5547634071</v>
+        <v>23027.86612230885</v>
       </c>
       <c r="H8" t="n">
-        <v>18635.8970836291</v>
+        <v>19926.84195719305</v>
       </c>
       <c r="I8" t="n">
-        <v>24381.28550837155</v>
+        <v>19846.2620853024</v>
       </c>
       <c r="J8" t="n">
-        <v>23963.5155226302</v>
+        <v>22248.60827220735</v>
       </c>
       <c r="K8" t="n">
-        <v>22941.4389714378</v>
+        <v>22013.3275329385</v>
       </c>
       <c r="L8" t="n">
-        <v>15122.83299964635</v>
+        <v>21613.9154939796</v>
       </c>
       <c r="M8" t="n">
-        <v>15964.7985689247</v>
+        <v>33648.93092263835</v>
       </c>
       <c r="N8" t="n">
-        <v>21954.4964749759</v>
+        <v>35053.19221457405</v>
       </c>
       <c r="O8" t="n">
-        <v>22969.6396795448</v>
+        <v>31628.8477040085</v>
       </c>
       <c r="P8" t="n">
-        <v>19710.8129657384</v>
+        <v>37616.85305198095</v>
       </c>
       <c r="Q8" t="n">
-        <v>19772.9461126593</v>
+        <v>17700.2735157754</v>
       </c>
       <c r="R8" t="n">
-        <v>22192.36180382045</v>
+        <v>39187.79274214256</v>
       </c>
       <c r="S8" t="n">
-        <v>21972.5679822275</v>
+        <v>39966.5718136762</v>
       </c>
       <c r="T8" t="n">
-        <v>21455.9617009573</v>
+        <v>31186.9872460531</v>
       </c>
       <c r="U8" t="n">
-        <v>33524.82508097305</v>
+        <v>37752.65265688235</v>
       </c>
       <c r="V8" t="n">
-        <v>34995.67803892875</v>
+        <v>38654.47987959085</v>
       </c>
       <c r="W8" t="n">
-        <v>31255.16922470855</v>
+        <v>35067.25445316115</v>
       </c>
       <c r="X8" t="n">
-        <v>37428.3767000022</v>
+        <v>21506.47875430065</v>
       </c>
       <c r="Y8" t="n">
-        <v>39103.0583392229</v>
+        <v>27969.35883558795</v>
       </c>
       <c r="Z8" t="n">
-        <v>39641.05297196111</v>
+        <v>18372.4025428702</v>
       </c>
       <c r="AA8" t="n">
-        <v>30999.12904895455</v>
+        <v>28640.52920546015</v>
       </c>
       <c r="AB8" t="n">
-        <v>37375.6958246628</v>
+        <v>19058.0786625207</v>
       </c>
       <c r="AC8" t="n">
-        <v>38463.622489347</v>
+        <v>27786.2558952638</v>
       </c>
       <c r="AD8" t="n">
-        <v>34623.35397996476</v>
+        <v>31573.76727096955</v>
       </c>
       <c r="AE8" t="n">
-        <v>21454.49190460345</v>
+        <v>37809.37527106685</v>
       </c>
       <c r="AF8" t="n">
-        <v>27907.9610106319</v>
+        <v>34124.092195314</v>
       </c>
       <c r="AG8" t="n">
-        <v>18169.5295278442</v>
+        <v>32649.78055044255</v>
       </c>
       <c r="AH8" t="n">
-        <v>28360.37000808385</v>
+        <v>30049.52344707005</v>
       </c>
       <c r="AI8" t="n">
-        <v>27654.3799284192</v>
+        <v>30619.07768207255</v>
       </c>
       <c r="AJ8" t="n">
-        <v>31482.892069442</v>
+        <v>22502.82343902835</v>
       </c>
       <c r="AK8" t="n">
-        <v>37549.47926332404</v>
+        <v>28000.0519628225</v>
       </c>
       <c r="AL8" t="n">
-        <v>33928.98227626435</v>
+        <v>24930.3631779884</v>
       </c>
       <c r="AM8" t="n">
-        <v>32445.7307693277</v>
+        <v>24465.6044346989</v>
       </c>
       <c r="AN8" t="n">
-        <v>29680.74692954965</v>
+        <v>41424.3093516098</v>
       </c>
       <c r="AO8" t="n">
-        <v>30494.5329977343</v>
+        <v>35633.0089782238</v>
       </c>
       <c r="AP8" t="n">
-        <v>22467.2991333637</v>
+        <v>34978.26299385385</v>
       </c>
       <c r="AQ8" t="n">
-        <v>27684.01901972245</v>
+        <v>24156.1368434947</v>
       </c>
       <c r="AR8" t="n">
-        <v>24771.36400683615</v>
+        <v>23240.25844766395</v>
       </c>
       <c r="AS8" t="n">
-        <v>40609.48305534615</v>
+        <v>15294.15158790585</v>
       </c>
       <c r="AT8" t="n">
-        <v>35016.09468676989</v>
+        <v>16204.82976138565</v>
       </c>
       <c r="AU8" t="n">
-        <v>34872.7198678155</v>
+        <v>22008.7041769749</v>
       </c>
       <c r="AV8" t="n">
         <v>58938.8195</v>
@@ -2428,31 +2428,31 @@
         <v>31746.90135544375</v>
       </c>
       <c r="BQ8" t="n">
-        <v>66046.29449421521</v>
+        <v>66643.05595088392</v>
       </c>
       <c r="BR8" t="n">
-        <v>66704.75722169633</v>
+        <v>68071.85131709668</v>
       </c>
       <c r="BS8" t="n">
-        <v>79159.61374579441</v>
+        <v>80363.27247594061</v>
       </c>
       <c r="BT8" t="n">
-        <v>85452.05509517266</v>
+        <v>88098.34850070131</v>
       </c>
       <c r="BU8" t="n">
-        <v>64971.29226966516</v>
+        <v>66910.48043416067</v>
       </c>
       <c r="BV8" t="n">
-        <v>76318.50865996671</v>
+        <v>78329.48385828419</v>
       </c>
       <c r="BW8" t="n">
-        <v>79502.08765670167</v>
+        <v>80666.44555846317</v>
       </c>
       <c r="BX8" t="n">
-        <v>77635.48292601698</v>
+        <v>79466.01860303471</v>
       </c>
       <c r="BY8" t="n">
-        <v>67920.31197821039</v>
+        <v>68592.90438773579</v>
       </c>
     </row>
     <row r="9">
@@ -2477,127 +2477,127 @@
         <v>1698316.65470918</v>
       </c>
       <c r="G9" t="n">
+        <v>1953657.1430926</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2014199.06168294</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1790822.73193406</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1443755.52817518</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1564591.58663698</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1970313.74127984</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2470661.90715718</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2527283.75416462</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2105847.42581576</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2421202.90838998</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1466816.39147648</v>
       </c>
-      <c r="H9" t="n">
+      <c r="R9" t="n">
+        <v>2861788.170666261</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2785112.37681754</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5038810.982452061</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5636538.305159081</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6049808.34863592</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3456150.8082959</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1599383.84789106</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2408499.85809554</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1153911.62847246</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1847383.16277328</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1924986.18972528</v>
       </c>
-      <c r="I9" t="n">
+      <c r="AC9" t="n">
+        <v>1963689.22389178</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2583918.8280532</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3856207.218654341</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2799825.38531674</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3081100.34485264</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2326375.29938</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1977546.07586316</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2151719.3254238</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>3293436.0035962</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1824004.88094594</v>
+      </c>
+      <c r="AM9" t="n">
         <v>2693794.69019408</v>
       </c>
-      <c r="J9" t="n">
+      <c r="AN9" t="n">
+        <v>2287799.90739608</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>3008709.25558984</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2736623.22405714</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>3265940.9522993</v>
       </c>
-      <c r="K9" t="n">
+      <c r="AR9" t="n">
         <v>2398317.22903388</v>
       </c>
-      <c r="L9" t="n">
+      <c r="AS9" t="n">
         <v>1673813.56260536</v>
       </c>
-      <c r="M9" t="n">
+      <c r="AT9" t="n">
         <v>1671361.1306579</v>
       </c>
-      <c r="N9" t="n">
+      <c r="AU9" t="n">
         <v>1447457.46153008</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1953657.1430926</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2014199.06168294</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1790822.73193406</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1443755.52817518</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1564591.58663698</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1970313.74127984</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2470661.90715718</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2527283.75416462</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2105847.42581576</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2421202.90838998</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2861788.170666261</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2785112.37681754</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>5038810.982452061</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>5636538.305159081</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>6049808.34863592</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3456150.8082959</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1599383.84789106</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2408499.85809554</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1153911.62847246</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1847383.16277328</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1963689.22389178</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2583918.8280532</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>3856207.218654341</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2799825.38531674</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>3081100.34485264</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>2326375.29938</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1977546.07586316</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2151719.3254238</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>3293436.0035962</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1824004.88094594</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2287799.90739608</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3008709.25558984</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2736623.22405714</v>
       </c>
       <c r="AV9" t="n">
         <v>2040565.936933333</v>
@@ -2672,22 +2672,22 @@
         <v>2186908.808510384</v>
       </c>
       <c r="BT9" t="n">
-        <v>1526611.414481163</v>
+        <v>1465364.870438074</v>
       </c>
       <c r="BU9" t="n">
-        <v>1197000.573967651</v>
+        <v>1073011.442711933</v>
       </c>
       <c r="BV9" t="n">
-        <v>1459414.066163923</v>
+        <v>1145706.187841673</v>
       </c>
       <c r="BW9" t="n">
-        <v>1515763.911566187</v>
+        <v>1027047.573270711</v>
       </c>
       <c r="BX9" t="n">
-        <v>1527797.363900427</v>
+        <v>1107606.637430847</v>
       </c>
       <c r="BY9" t="n">
-        <v>1382972.910274663</v>
+        <v>1026338.674711787</v>
       </c>
     </row>
   </sheetData>

--- a/data/proteomics/protein_copy_statistical_top1000.xlsx
+++ b/data/proteomics/protein_copy_statistical_top1000.xlsx
@@ -425,63 +425,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>maltose(mmol/gDW)</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>oleate(mmol/gDW)</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>fructose(mmol/gDW)</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>sucrose(mmol/gDW)</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>trehalose(mmol/gDW)</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>lactate(mmol/gDW)</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>acetate(mmol/gDW)</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>pryuvate(mmol/gDW)</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>glycerol(mmol/gDW)</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>galactose(mmol/gDW)</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>raffinose(mmol/gDW)</t>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>S19</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>S30</t>
         </is>
       </c>
     </row>
@@ -524,6 +619,63 @@
       <c r="L2" t="n">
         <v>1000</v>
       </c>
+      <c r="M2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -532,37 +684,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90101.44000503165</v>
+        <v>53961.84764404355</v>
       </c>
       <c r="C3" t="n">
-        <v>96854.03285125572</v>
+        <v>53887.28269345002</v>
       </c>
       <c r="D3" t="n">
-        <v>94457.19510634952</v>
+        <v>54221.30705028991</v>
       </c>
       <c r="E3" t="n">
-        <v>93152.28167818206</v>
+        <v>53583.91866205424</v>
       </c>
       <c r="F3" t="n">
-        <v>88158.12718218745</v>
+        <v>53369.36527147247</v>
       </c>
       <c r="G3" t="n">
-        <v>89381.54119445605</v>
+        <v>53898.87888455768</v>
       </c>
       <c r="H3" t="n">
-        <v>111204.999221424</v>
+        <v>51167.38577257958</v>
       </c>
       <c r="I3" t="n">
-        <v>101383.8587757529</v>
+        <v>51027.74398050865</v>
       </c>
       <c r="J3" t="n">
-        <v>92404.16145146871</v>
+        <v>50580.14890719364</v>
       </c>
       <c r="K3" t="n">
-        <v>77364.13511731174</v>
+        <v>50884.7363428539</v>
       </c>
       <c r="L3" t="n">
-        <v>76779.49436118959</v>
+        <v>50579.73273346649</v>
+      </c>
+      <c r="M3" t="n">
+        <v>50537.81891360775</v>
+      </c>
+      <c r="N3" t="n">
+        <v>50803.23618690298</v>
+      </c>
+      <c r="O3" t="n">
+        <v>50176.99015135462</v>
+      </c>
+      <c r="P3" t="n">
+        <v>50925.46986474168</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>50183.91739352087</v>
+      </c>
+      <c r="R3" t="n">
+        <v>50515.74258167564</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50290.36927225749</v>
+      </c>
+      <c r="T3" t="n">
+        <v>51584.95307900145</v>
+      </c>
+      <c r="U3" t="n">
+        <v>51740.74043603657</v>
+      </c>
+      <c r="V3" t="n">
+        <v>52172.64073484235</v>
+      </c>
+      <c r="W3" t="n">
+        <v>51323.74274819736</v>
+      </c>
+      <c r="X3" t="n">
+        <v>50935.15465363812</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>51533.11462250933</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>50414.24526446268</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>50313.48094978404</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>49898.79889138372</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>50902.78895270527</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>50927.36956037561</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>51247.67675532372</v>
       </c>
     </row>
     <row r="4">
@@ -572,37 +781,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>235844.3691802917</v>
+        <v>136445.2604157887</v>
       </c>
       <c r="C4" t="n">
-        <v>256839.1586328733</v>
+        <v>136332.5725233177</v>
       </c>
       <c r="D4" t="n">
-        <v>303522.404038647</v>
+        <v>135066.8628058252</v>
       </c>
       <c r="E4" t="n">
-        <v>302646.485228717</v>
+        <v>133867.1863666313</v>
       </c>
       <c r="F4" t="n">
-        <v>224894.6025179674</v>
+        <v>134415.6344133083</v>
       </c>
       <c r="G4" t="n">
-        <v>225430.4516058913</v>
+        <v>134570.4082710276</v>
       </c>
       <c r="H4" t="n">
-        <v>309924.7517149917</v>
+        <v>132226.2544825127</v>
       </c>
       <c r="I4" t="n">
-        <v>300498.114570479</v>
+        <v>130802.1956774623</v>
       </c>
       <c r="J4" t="n">
-        <v>238538.4729674571</v>
+        <v>130929.9813604919</v>
       </c>
       <c r="K4" t="n">
-        <v>286538.3824025185</v>
+        <v>130181.3023532971</v>
       </c>
       <c r="L4" t="n">
-        <v>256929.2838757988</v>
+        <v>130750.492088267</v>
+      </c>
+      <c r="M4" t="n">
+        <v>130116.5828803086</v>
+      </c>
+      <c r="N4" t="n">
+        <v>131369.0592825588</v>
+      </c>
+      <c r="O4" t="n">
+        <v>129551.9826267713</v>
+      </c>
+      <c r="P4" t="n">
+        <v>131743.6562965913</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>129649.1902560207</v>
+      </c>
+      <c r="R4" t="n">
+        <v>130572.1689684314</v>
+      </c>
+      <c r="S4" t="n">
+        <v>129082.5821799394</v>
+      </c>
+      <c r="T4" t="n">
+        <v>134221.2348329227</v>
+      </c>
+      <c r="U4" t="n">
+        <v>133937.4662409066</v>
+      </c>
+      <c r="V4" t="n">
+        <v>135047.6257298692</v>
+      </c>
+      <c r="W4" t="n">
+        <v>134442.1311725319</v>
+      </c>
+      <c r="X4" t="n">
+        <v>134783.339035592</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>136792.3076316702</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>131377.3734367275</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>130728.4136759442</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>131779.7891298767</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>130854.6798121647</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>130880.9337183899</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>132048.8335992743</v>
       </c>
     </row>
     <row r="5">
@@ -612,37 +878,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4421.530275530009</v>
+        <v>2316.278221467924</v>
       </c>
       <c r="C5" t="n">
-        <v>4852.60400171739</v>
+        <v>2293.527867639348</v>
       </c>
       <c r="D5" t="n">
-        <v>4477.84777579591</v>
+        <v>2371.993054379471</v>
       </c>
       <c r="E5" t="n">
-        <v>4653.473496658243</v>
+        <v>2458.538444364563</v>
       </c>
       <c r="F5" t="n">
-        <v>4875.714087512352</v>
+        <v>2293.728412492208</v>
       </c>
       <c r="G5" t="n">
-        <v>4799.42148568716</v>
+        <v>2293.595159287991</v>
       </c>
       <c r="H5" t="n">
-        <v>4852.291779119411</v>
+        <v>2189.778729115879</v>
       </c>
       <c r="I5" t="n">
-        <v>5029.373510375292</v>
+        <v>2274.356174093468</v>
       </c>
       <c r="J5" t="n">
-        <v>5230.576827930286</v>
+        <v>2251.408123044189</v>
       </c>
       <c r="K5" t="n">
-        <v>4583.52085475708</v>
+        <v>2224.359741755633</v>
       </c>
       <c r="L5" t="n">
-        <v>4343.062933130394</v>
+        <v>2256.385000273141</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2204.253624851572</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2220.311946935704</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2327.416205150605</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2309.627125034842</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2208.494898342872</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2232.045439192961</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2280.130335996203</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2262.668598316928</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2241.0873205885</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2297.738257087294</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2296.905280766523</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2168.84511261133</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2246.27308099853</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2235.671301836055</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2319.222852398061</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2067.624379909287</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2255.125531872553</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2301.483242351431</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2246.090507984815</v>
       </c>
     </row>
     <row r="6">
@@ -652,37 +975,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7705.257432622958</v>
+        <v>4194.014078599545</v>
       </c>
       <c r="C6" t="n">
-        <v>8318.969541618622</v>
+        <v>4166.826820190783</v>
       </c>
       <c r="D6" t="n">
-        <v>7911.487875853649</v>
+        <v>4336.180781579811</v>
       </c>
       <c r="E6" t="n">
-        <v>7922.844200489174</v>
+        <v>4390.033535419529</v>
       </c>
       <c r="F6" t="n">
-        <v>8427.832982481199</v>
+        <v>4212.738286915213</v>
       </c>
       <c r="G6" t="n">
-        <v>8199.858264315415</v>
+        <v>4171.140882902947</v>
       </c>
       <c r="H6" t="n">
-        <v>8614.122202285856</v>
+        <v>4180.189217118312</v>
       </c>
       <c r="I6" t="n">
-        <v>8770.851122319431</v>
+        <v>4218.332604230885</v>
       </c>
       <c r="J6" t="n">
-        <v>8605.185852087463</v>
+        <v>4206.876442473074</v>
       </c>
       <c r="K6" t="n">
-        <v>7461.186885505573</v>
+        <v>4226.353118522915</v>
       </c>
       <c r="L6" t="n">
-        <v>7178.439500410393</v>
+        <v>4204.723831319343</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4175.348823136403</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4131.176642214513</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4175.626296304819</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4074.168747705939</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4099.07904114195</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4153.246765817798</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4221.770660440898</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4100.845690538994</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4047.160350165125</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4119.767970697961</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4078.941935531634</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4012.528928971745</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4163.451880125787</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4112.693270353568</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4222.987810436121</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3886.723753019472</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4045.089989807308</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4118.384305668032</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>4294.274452562547</v>
       </c>
     </row>
     <row r="7">
@@ -692,37 +1072,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18033.36240866197</v>
+        <v>9317.491800008571</v>
       </c>
       <c r="C7" t="n">
-        <v>18348.04606612602</v>
+        <v>9699.141740418556</v>
       </c>
       <c r="D7" t="n">
-        <v>15534.60128983051</v>
+        <v>9761.824236062437</v>
       </c>
       <c r="E7" t="n">
-        <v>15518.03783936034</v>
+        <v>9616.578020200232</v>
       </c>
       <c r="F7" t="n">
-        <v>18413.23785794818</v>
+        <v>9588.868607227138</v>
       </c>
       <c r="G7" t="n">
-        <v>17869.46442402063</v>
+        <v>9367.185029792709</v>
       </c>
       <c r="H7" t="n">
-        <v>18842.17553419524</v>
+        <v>9551.477483884286</v>
       </c>
       <c r="I7" t="n">
-        <v>18039.89069266979</v>
+        <v>9656.733957020617</v>
       </c>
       <c r="J7" t="n">
-        <v>18034.2121570603</v>
+        <v>9624.340958584831</v>
       </c>
       <c r="K7" t="n">
-        <v>14332.44107385187</v>
+        <v>9708.588814468625</v>
       </c>
       <c r="L7" t="n">
-        <v>13675.61473580465</v>
+        <v>9664.968692291137</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9605.693822216659</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9826.350931186844</v>
+      </c>
+      <c r="O7" t="n">
+        <v>9601.165536086268</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9599.582534423671</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9322.611786903704</v>
+      </c>
+      <c r="R7" t="n">
+        <v>9649.732999369433</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9806.451559059849</v>
+      </c>
+      <c r="T7" t="n">
+        <v>9183.076309598353</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9311.395512002135</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9352.996071309062</v>
+      </c>
+      <c r="W7" t="n">
+        <v>9369.295568241076</v>
+      </c>
+      <c r="X7" t="n">
+        <v>9390.863459610351</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9418.184868097938</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9267.999268526644</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9460.481126584069</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8869.324891569529</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9171.148613723795</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>9382.163425128048</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9550.244677913854</v>
       </c>
     </row>
     <row r="8">
@@ -732,37 +1169,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55375.63500668944</v>
+        <v>29175.79320891272</v>
       </c>
       <c r="C8" t="n">
-        <v>59500.45153850355</v>
+        <v>29575.13214075504</v>
       </c>
       <c r="D8" t="n">
-        <v>43554.77528704338</v>
+        <v>29646.62590185027</v>
       </c>
       <c r="E8" t="n">
-        <v>44598.01381791079</v>
+        <v>29893.05424704065</v>
       </c>
       <c r="F8" t="n">
-        <v>57644.2969655563</v>
+        <v>29290.95251706533</v>
       </c>
       <c r="G8" t="n">
-        <v>57419.63754724183</v>
+        <v>29514.35199713381</v>
       </c>
       <c r="H8" t="n">
-        <v>54617.01279702976</v>
+        <v>29100.11937506474</v>
       </c>
       <c r="I8" t="n">
-        <v>60695.8389664479</v>
+        <v>29645.75198190197</v>
       </c>
       <c r="J8" t="n">
-        <v>53458.79675728663</v>
+        <v>29483.06469657754</v>
       </c>
       <c r="K8" t="n">
-        <v>41272.63425310593</v>
+        <v>28954.96123692625</v>
       </c>
       <c r="L8" t="n">
-        <v>39662.3256685274</v>
+        <v>29663.47329714863</v>
+      </c>
+      <c r="M8" t="n">
+        <v>28954.64382409313</v>
+      </c>
+      <c r="N8" t="n">
+        <v>28801.93890712671</v>
+      </c>
+      <c r="O8" t="n">
+        <v>29398.8481100575</v>
+      </c>
+      <c r="P8" t="n">
+        <v>29205.16604938886</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>28665.77322207024</v>
+      </c>
+      <c r="R8" t="n">
+        <v>29061.06317026683</v>
+      </c>
+      <c r="S8" t="n">
+        <v>29198.77163304486</v>
+      </c>
+      <c r="T8" t="n">
+        <v>28670.45473964619</v>
+      </c>
+      <c r="U8" t="n">
+        <v>29163.57884828288</v>
+      </c>
+      <c r="V8" t="n">
+        <v>29030.27931299276</v>
+      </c>
+      <c r="W8" t="n">
+        <v>28196.86515951489</v>
+      </c>
+      <c r="X8" t="n">
+        <v>28608.47157676085</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>28651.20917432538</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>28453.45335937301</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>28904.54461297661</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>27143.50679916269</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>29029.0519879054</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>28683.24863678216</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>29527.01372515827</v>
       </c>
     </row>
     <row r="9">
@@ -772,37 +1266,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3441293.778590984</v>
+        <v>1943049.664115919</v>
       </c>
       <c r="C9" t="n">
-        <v>2997519.452074238</v>
+        <v>1983105.574626185</v>
       </c>
       <c r="D9" t="n">
-        <v>3474572.365462308</v>
+        <v>1914430.095727566</v>
       </c>
       <c r="E9" t="n">
-        <v>3766905.59001234</v>
+        <v>1945154.819028278</v>
       </c>
       <c r="F9" t="n">
-        <v>2753403.630072502</v>
+        <v>1998587.776671322</v>
       </c>
       <c r="G9" t="n">
-        <v>2173211.290130805</v>
+        <v>1918674.373789614</v>
       </c>
       <c r="H9" t="n">
-        <v>3039979.376189653</v>
+        <v>2137465.011001145</v>
       </c>
       <c r="I9" t="n">
-        <v>6004868.809911354</v>
+        <v>2124551.042110998</v>
       </c>
       <c r="J9" t="n">
-        <v>2247437.265527637</v>
+        <v>2151800.826652864</v>
       </c>
       <c r="K9" t="n">
-        <v>5375654.536827597</v>
+        <v>2105580.175655238</v>
       </c>
       <c r="L9" t="n">
-        <v>4239740.357313359</v>
+        <v>2171133.869241349</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2100201.602780261</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2169433.580600113</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2150009.559917057</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2200059.489675947</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2112649.063402391</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2130198.594493009</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2132771.306836835</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2192154.428067199</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2172264.044427255</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2155059.709455179</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2208836.99664789</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2263723.472387413</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2363332.081626541</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2209963.484593864</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2183302.056370241</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2173948.79615762</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2093456.443268903</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2121380.719582611</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2165432.92409642</v>
       </c>
     </row>
   </sheetData>

--- a/data/proteomics/protein_copy_statistical_top1000.xlsx
+++ b/data/proteomics/protein_copy_statistical_top1000.xlsx
@@ -425,158 +425,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>maltose(mmol/gDW)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>oleate(mmol/gDW)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>fructose(mmol/gDW)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>sucrose(mmol/gDW)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>trehalose(mmol/gDW)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>lactate(mmol/gDW)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>acetate(mmol/gDW)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>pryuvate(mmol/gDW)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>glycerol(mmol/gDW)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>galactose(mmol/gDW)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>S11</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>S13</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>S14</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>S15</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>S16</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>S17</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>S18</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>S19</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>S20</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>S21</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S22</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>S23</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>S24</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>S25</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>S26</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>S27</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>S28</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>S29</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>S30</t>
+          <t>raffinose(mmol/gDW)</t>
         </is>
       </c>
     </row>
@@ -619,63 +524,6 @@
       <c r="L2" t="n">
         <v>1000</v>
       </c>
-      <c r="M2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -684,94 +532,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53961.84764404355</v>
+        <v>90101.44000503165</v>
       </c>
       <c r="C3" t="n">
-        <v>53887.28269345002</v>
+        <v>96854.03285125572</v>
       </c>
       <c r="D3" t="n">
-        <v>54221.30705028991</v>
+        <v>94457.19510634952</v>
       </c>
       <c r="E3" t="n">
-        <v>53583.91866205424</v>
+        <v>93152.28167818206</v>
       </c>
       <c r="F3" t="n">
-        <v>53369.36527147247</v>
+        <v>88158.12718218745</v>
       </c>
       <c r="G3" t="n">
-        <v>53898.87888455768</v>
+        <v>89381.54119445605</v>
       </c>
       <c r="H3" t="n">
-        <v>51167.38577257958</v>
+        <v>111204.999221424</v>
       </c>
       <c r="I3" t="n">
-        <v>51027.74398050865</v>
+        <v>101383.8587757529</v>
       </c>
       <c r="J3" t="n">
-        <v>50580.14890719364</v>
+        <v>92404.16145146871</v>
       </c>
       <c r="K3" t="n">
-        <v>50884.7363428539</v>
+        <v>77364.13511731174</v>
       </c>
       <c r="L3" t="n">
-        <v>50579.73273346649</v>
-      </c>
-      <c r="M3" t="n">
-        <v>50537.81891360775</v>
-      </c>
-      <c r="N3" t="n">
-        <v>50803.23618690298</v>
-      </c>
-      <c r="O3" t="n">
-        <v>50176.99015135462</v>
-      </c>
-      <c r="P3" t="n">
-        <v>50925.46986474168</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>50183.91739352087</v>
-      </c>
-      <c r="R3" t="n">
-        <v>50515.74258167564</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50290.36927225749</v>
-      </c>
-      <c r="T3" t="n">
-        <v>51584.95307900145</v>
-      </c>
-      <c r="U3" t="n">
-        <v>51740.74043603657</v>
-      </c>
-      <c r="V3" t="n">
-        <v>52172.64073484235</v>
-      </c>
-      <c r="W3" t="n">
-        <v>51323.74274819736</v>
-      </c>
-      <c r="X3" t="n">
-        <v>50935.15465363812</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>51533.11462250933</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>50414.24526446268</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>50313.48094978404</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>49898.79889138372</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>50902.78895270527</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>50927.36956037561</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>51247.67675532372</v>
+        <v>76779.49436118959</v>
       </c>
     </row>
     <row r="4">
@@ -781,94 +572,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>136445.2604157887</v>
+        <v>235844.3691802917</v>
       </c>
       <c r="C4" t="n">
-        <v>136332.5725233177</v>
+        <v>256839.1586328733</v>
       </c>
       <c r="D4" t="n">
-        <v>135066.8628058252</v>
+        <v>303522.404038647</v>
       </c>
       <c r="E4" t="n">
-        <v>133867.1863666313</v>
+        <v>302646.485228717</v>
       </c>
       <c r="F4" t="n">
-        <v>134415.6344133083</v>
+        <v>224894.6025179674</v>
       </c>
       <c r="G4" t="n">
-        <v>134570.4082710276</v>
+        <v>225430.4516058913</v>
       </c>
       <c r="H4" t="n">
-        <v>132226.2544825127</v>
+        <v>309924.7517149917</v>
       </c>
       <c r="I4" t="n">
-        <v>130802.1956774623</v>
+        <v>300498.114570479</v>
       </c>
       <c r="J4" t="n">
-        <v>130929.9813604919</v>
+        <v>238538.4729674571</v>
       </c>
       <c r="K4" t="n">
-        <v>130181.3023532971</v>
+        <v>286538.3824025185</v>
       </c>
       <c r="L4" t="n">
-        <v>130750.492088267</v>
-      </c>
-      <c r="M4" t="n">
-        <v>130116.5828803086</v>
-      </c>
-      <c r="N4" t="n">
-        <v>131369.0592825588</v>
-      </c>
-      <c r="O4" t="n">
-        <v>129551.9826267713</v>
-      </c>
-      <c r="P4" t="n">
-        <v>131743.6562965913</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>129649.1902560207</v>
-      </c>
-      <c r="R4" t="n">
-        <v>130572.1689684314</v>
-      </c>
-      <c r="S4" t="n">
-        <v>129082.5821799394</v>
-      </c>
-      <c r="T4" t="n">
-        <v>134221.2348329227</v>
-      </c>
-      <c r="U4" t="n">
-        <v>133937.4662409066</v>
-      </c>
-      <c r="V4" t="n">
-        <v>135047.6257298692</v>
-      </c>
-      <c r="W4" t="n">
-        <v>134442.1311725319</v>
-      </c>
-      <c r="X4" t="n">
-        <v>134783.339035592</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>136792.3076316702</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>131377.3734367275</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>130728.4136759442</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>131779.7891298767</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>130854.6798121647</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>130880.9337183899</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>132048.8335992743</v>
+        <v>256929.2838757988</v>
       </c>
     </row>
     <row r="5">
@@ -878,94 +612,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2316.278221467924</v>
+        <v>4421.530275530009</v>
       </c>
       <c r="C5" t="n">
-        <v>2293.527867639348</v>
+        <v>4852.60400171739</v>
       </c>
       <c r="D5" t="n">
-        <v>2371.993054379471</v>
+        <v>4477.84777579591</v>
       </c>
       <c r="E5" t="n">
-        <v>2458.538444364563</v>
+        <v>4653.473496658243</v>
       </c>
       <c r="F5" t="n">
-        <v>2293.728412492208</v>
+        <v>4875.714087512352</v>
       </c>
       <c r="G5" t="n">
-        <v>2293.595159287991</v>
+        <v>4799.42148568716</v>
       </c>
       <c r="H5" t="n">
-        <v>2189.778729115879</v>
+        <v>4852.291779119411</v>
       </c>
       <c r="I5" t="n">
-        <v>2274.356174093468</v>
+        <v>5029.373510375292</v>
       </c>
       <c r="J5" t="n">
-        <v>2251.408123044189</v>
+        <v>5230.576827930286</v>
       </c>
       <c r="K5" t="n">
-        <v>2224.359741755633</v>
+        <v>4583.52085475708</v>
       </c>
       <c r="L5" t="n">
-        <v>2256.385000273141</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2204.253624851572</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2220.311946935704</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2327.416205150605</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2309.627125034842</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2208.494898342872</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2232.045439192961</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2280.130335996203</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2262.668598316928</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2241.0873205885</v>
-      </c>
-      <c r="V5" t="n">
-        <v>2297.738257087294</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2296.905280766523</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2168.84511261133</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2246.27308099853</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2235.671301836055</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2319.222852398061</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2067.624379909287</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2255.125531872553</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2301.483242351431</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2246.090507984815</v>
+        <v>4343.062933130394</v>
       </c>
     </row>
     <row r="6">
@@ -975,94 +652,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4194.014078599545</v>
+        <v>7705.257432622958</v>
       </c>
       <c r="C6" t="n">
-        <v>4166.826820190783</v>
+        <v>8318.969541618622</v>
       </c>
       <c r="D6" t="n">
-        <v>4336.180781579811</v>
+        <v>7911.487875853649</v>
       </c>
       <c r="E6" t="n">
-        <v>4390.033535419529</v>
+        <v>7922.844200489174</v>
       </c>
       <c r="F6" t="n">
-        <v>4212.738286915213</v>
+        <v>8427.832982481199</v>
       </c>
       <c r="G6" t="n">
-        <v>4171.140882902947</v>
+        <v>8199.858264315415</v>
       </c>
       <c r="H6" t="n">
-        <v>4180.189217118312</v>
+        <v>8614.122202285856</v>
       </c>
       <c r="I6" t="n">
-        <v>4218.332604230885</v>
+        <v>8770.851122319431</v>
       </c>
       <c r="J6" t="n">
-        <v>4206.876442473074</v>
+        <v>8605.185852087463</v>
       </c>
       <c r="K6" t="n">
-        <v>4226.353118522915</v>
+        <v>7461.186885505573</v>
       </c>
       <c r="L6" t="n">
-        <v>4204.723831319343</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4175.348823136403</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4131.176642214513</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4175.626296304819</v>
-      </c>
-      <c r="P6" t="n">
-        <v>4074.168747705939</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4099.07904114195</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4153.246765817798</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4221.770660440898</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4100.845690538994</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4047.160350165125</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4119.767970697961</v>
-      </c>
-      <c r="W6" t="n">
-        <v>4078.941935531634</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4012.528928971745</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>4163.451880125787</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4112.693270353568</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4222.987810436121</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3886.723753019472</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4045.089989807308</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>4118.384305668032</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>4294.274452562547</v>
+        <v>7178.439500410393</v>
       </c>
     </row>
     <row r="7">
@@ -1072,94 +692,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9317.491800008571</v>
+        <v>18033.36240866197</v>
       </c>
       <c r="C7" t="n">
-        <v>9699.141740418556</v>
+        <v>18348.04606612602</v>
       </c>
       <c r="D7" t="n">
-        <v>9761.824236062437</v>
+        <v>15534.60128983051</v>
       </c>
       <c r="E7" t="n">
-        <v>9616.578020200232</v>
+        <v>15518.03783936034</v>
       </c>
       <c r="F7" t="n">
-        <v>9588.868607227138</v>
+        <v>18413.23785794818</v>
       </c>
       <c r="G7" t="n">
-        <v>9367.185029792709</v>
+        <v>17869.46442402063</v>
       </c>
       <c r="H7" t="n">
-        <v>9551.477483884286</v>
+        <v>18842.17553419524</v>
       </c>
       <c r="I7" t="n">
-        <v>9656.733957020617</v>
+        <v>18039.89069266979</v>
       </c>
       <c r="J7" t="n">
-        <v>9624.340958584831</v>
+        <v>18034.2121570603</v>
       </c>
       <c r="K7" t="n">
-        <v>9708.588814468625</v>
+        <v>14332.44107385187</v>
       </c>
       <c r="L7" t="n">
-        <v>9664.968692291137</v>
-      </c>
-      <c r="M7" t="n">
-        <v>9605.693822216659</v>
-      </c>
-      <c r="N7" t="n">
-        <v>9826.350931186844</v>
-      </c>
-      <c r="O7" t="n">
-        <v>9601.165536086268</v>
-      </c>
-      <c r="P7" t="n">
-        <v>9599.582534423671</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>9322.611786903704</v>
-      </c>
-      <c r="R7" t="n">
-        <v>9649.732999369433</v>
-      </c>
-      <c r="S7" t="n">
-        <v>9806.451559059849</v>
-      </c>
-      <c r="T7" t="n">
-        <v>9183.076309598353</v>
-      </c>
-      <c r="U7" t="n">
-        <v>9311.395512002135</v>
-      </c>
-      <c r="V7" t="n">
-        <v>9352.996071309062</v>
-      </c>
-      <c r="W7" t="n">
-        <v>9369.295568241076</v>
-      </c>
-      <c r="X7" t="n">
-        <v>9390.863459610351</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>9418.184868097938</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>9267.999268526644</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>9460.481126584069</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>8869.324891569529</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9171.148613723795</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>9382.163425128048</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>9550.244677913854</v>
+        <v>13675.61473580465</v>
       </c>
     </row>
     <row r="8">
@@ -1169,94 +732,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29175.79320891272</v>
+        <v>55375.63500668944</v>
       </c>
       <c r="C8" t="n">
-        <v>29575.13214075504</v>
+        <v>59500.45153850355</v>
       </c>
       <c r="D8" t="n">
-        <v>29646.62590185027</v>
+        <v>43554.77528704338</v>
       </c>
       <c r="E8" t="n">
-        <v>29893.05424704065</v>
+        <v>44598.01381791079</v>
       </c>
       <c r="F8" t="n">
-        <v>29290.95251706533</v>
+        <v>57644.2969655563</v>
       </c>
       <c r="G8" t="n">
-        <v>29514.35199713381</v>
+        <v>57419.63754724183</v>
       </c>
       <c r="H8" t="n">
-        <v>29100.11937506474</v>
+        <v>54617.01279702976</v>
       </c>
       <c r="I8" t="n">
-        <v>29645.75198190197</v>
+        <v>60695.8389664479</v>
       </c>
       <c r="J8" t="n">
-        <v>29483.06469657754</v>
+        <v>53458.79675728663</v>
       </c>
       <c r="K8" t="n">
-        <v>28954.96123692625</v>
+        <v>41272.63425310593</v>
       </c>
       <c r="L8" t="n">
-        <v>29663.47329714863</v>
-      </c>
-      <c r="M8" t="n">
-        <v>28954.64382409313</v>
-      </c>
-      <c r="N8" t="n">
-        <v>28801.93890712671</v>
-      </c>
-      <c r="O8" t="n">
-        <v>29398.8481100575</v>
-      </c>
-      <c r="P8" t="n">
-        <v>29205.16604938886</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>28665.77322207024</v>
-      </c>
-      <c r="R8" t="n">
-        <v>29061.06317026683</v>
-      </c>
-      <c r="S8" t="n">
-        <v>29198.77163304486</v>
-      </c>
-      <c r="T8" t="n">
-        <v>28670.45473964619</v>
-      </c>
-      <c r="U8" t="n">
-        <v>29163.57884828288</v>
-      </c>
-      <c r="V8" t="n">
-        <v>29030.27931299276</v>
-      </c>
-      <c r="W8" t="n">
-        <v>28196.86515951489</v>
-      </c>
-      <c r="X8" t="n">
-        <v>28608.47157676085</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>28651.20917432538</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>28453.45335937301</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>28904.54461297661</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>27143.50679916269</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>29029.0519879054</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>28683.24863678216</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>29527.01372515827</v>
+        <v>39662.3256685274</v>
       </c>
     </row>
     <row r="9">
@@ -1266,94 +772,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1943049.664115919</v>
+        <v>3441293.778590984</v>
       </c>
       <c r="C9" t="n">
-        <v>1983105.574626185</v>
+        <v>2997519.452074238</v>
       </c>
       <c r="D9" t="n">
-        <v>1914430.095727566</v>
+        <v>3474572.365462308</v>
       </c>
       <c r="E9" t="n">
-        <v>1945154.819028278</v>
+        <v>3766905.59001234</v>
       </c>
       <c r="F9" t="n">
-        <v>1998587.776671322</v>
+        <v>2753403.630072502</v>
       </c>
       <c r="G9" t="n">
-        <v>1918674.373789614</v>
+        <v>2173211.290130805</v>
       </c>
       <c r="H9" t="n">
-        <v>2137465.011001145</v>
+        <v>3039979.376189653</v>
       </c>
       <c r="I9" t="n">
-        <v>2124551.042110998</v>
+        <v>6004868.809911354</v>
       </c>
       <c r="J9" t="n">
-        <v>2151800.826652864</v>
+        <v>2247437.265527637</v>
       </c>
       <c r="K9" t="n">
-        <v>2105580.175655238</v>
+        <v>5375654.536827597</v>
       </c>
       <c r="L9" t="n">
-        <v>2171133.869241349</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2100201.602780261</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2169433.580600113</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2150009.559917057</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2200059.489675947</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2112649.063402391</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2130198.594493009</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2132771.306836835</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2192154.428067199</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2172264.044427255</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2155059.709455179</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2208836.99664789</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2263723.472387413</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2363332.081626541</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2209963.484593864</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2183302.056370241</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2173948.79615762</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2093456.443268903</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2121380.719582611</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2165432.92409642</v>
+        <v>4239740.357313359</v>
       </c>
     </row>
   </sheetData>

--- a/data/proteomics/protein_copy_statistical_top1000.xlsx
+++ b/data/proteomics/protein_copy_statistical_top1000.xlsx
@@ -425,63 +425,388 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:BY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>maltose(mmol/gDW)</t>
+          <t>Glucose_phase(mmol/gDW)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>oleate(mmol/gDW)</t>
+          <t>Diauxic_shift(mmol/gDW)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>fructose(mmol/gDW)</t>
+          <t>Ethanol_phase(mmol/gDW)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>sucrose(mmol/gDW)</t>
+          <t>mmol/gDW_carl</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>trehalose(mmol/gDW)</t>
+          <t>prot.1</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>lactate(mmol/gDW)</t>
+          <t>prot.10</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>acetate(mmol/gDW)</t>
+          <t>prot.11</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>pryuvate(mmol/gDW)</t>
+          <t>prot.12</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>glycerol(mmol/gDW)</t>
+          <t>prot.13</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>galactose(mmol/gDW)</t>
+          <t>prot.14</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>raffinose(mmol/gDW)</t>
+          <t>prot.15</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>prot.16</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>prot.17</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>prot.18</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>prot.19</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>prot.2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>prot.20</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>prot.21</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>prot.22</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>prot.23</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>prot.24</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>prot.25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>prot.26</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>prot.27</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>prot.28</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>prot.29</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>prot.3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>prot.30</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>prot.31</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>prot.32</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>prot.33</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>prot.34</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>prot.35</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>prot.36</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>prot.37</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>prot.38</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>prot.39</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>prot.4</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>prot.40</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>prot.41</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>prot.42</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>prot.5</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>prot.6</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>prot.7</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>prot.8</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>prot.9</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>mmol/gDW_Tyler_D0.1</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Min_ave_aerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Rich_ave_aerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Min_ave_anaerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Rich_ave_anaerobic(mmol/gDW)</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_REF_CN4_D=0.1</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_CN22_D=0.1</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_CN38_D=0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_CN75_D=0.1</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep1_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep2_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep3_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>FG_rep4_CN4_D= 0.26 or 0.32</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>molecular/cell_paxdb</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghaemmaghami et al. 2003 - Copy </t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Kulak et al. 2014 - Copy</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Copy number - Glucose</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Copy number - Galactose</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Copy number - Glycerol</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Mean molecules per cell_cell_system_2018</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Median molecules per cell_cell_system_2018</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.027_M</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.044_M</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.102_M</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.152_M</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.214_M</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.254_M</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.284_M</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.334_M</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>D=0.379_M</t>
         </is>
       </c>
     </row>
@@ -524,6 +849,201 @@
       <c r="L2" t="n">
         <v>1000</v>
       </c>
+      <c r="M2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -532,37 +1052,232 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90101.44000503165</v>
+        <v>118666.5729440651</v>
       </c>
       <c r="C3" t="n">
-        <v>96854.03285125572</v>
+        <v>106756.1964861159</v>
       </c>
       <c r="D3" t="n">
-        <v>94457.19510634952</v>
+        <v>92809.76170128527</v>
       </c>
       <c r="E3" t="n">
-        <v>93152.28167818206</v>
+        <v>105064.9080032164</v>
       </c>
       <c r="F3" t="n">
-        <v>88158.12718218745</v>
+        <v>38525.24155144845</v>
       </c>
       <c r="G3" t="n">
-        <v>89381.54119445605</v>
+        <v>43290.55543928633</v>
       </c>
       <c r="H3" t="n">
-        <v>111204.999221424</v>
+        <v>37038.66398542648</v>
       </c>
       <c r="I3" t="n">
-        <v>101383.8587757529</v>
+        <v>37049.69751370615</v>
       </c>
       <c r="J3" t="n">
-        <v>92404.16145146871</v>
+        <v>40837.33308003151</v>
       </c>
       <c r="K3" t="n">
-        <v>77364.13511731174</v>
+        <v>39847.60282598255</v>
       </c>
       <c r="L3" t="n">
-        <v>76779.49436118959</v>
+        <v>40191.2456289303</v>
+      </c>
+      <c r="M3" t="n">
+        <v>68185.90319859645</v>
+      </c>
+      <c r="N3" t="n">
+        <v>68300.36551275357</v>
+      </c>
+      <c r="O3" t="n">
+        <v>64551.27514691396</v>
+      </c>
+      <c r="P3" t="n">
+        <v>84920.98671372708</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>34692.25925999735</v>
+      </c>
+      <c r="R3" t="n">
+        <v>89688.82595623491</v>
+      </c>
+      <c r="S3" t="n">
+        <v>89382.30386128626</v>
+      </c>
+      <c r="T3" t="n">
+        <v>76680.59009819463</v>
+      </c>
+      <c r="U3" t="n">
+        <v>92755.48688594722</v>
+      </c>
+      <c r="V3" t="n">
+        <v>95245.92494849784</v>
+      </c>
+      <c r="W3" t="n">
+        <v>73108.65300605455</v>
+      </c>
+      <c r="X3" t="n">
+        <v>43121.54018601456</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>53696.50110002611</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>30859.44335696471</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>50471.21048951334</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>37166.90523415687</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>50108.08483965501</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>58123.26071996987</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>72325.18520311838</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>62102.80501737414</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>58411.01551273657</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>52606.25504036327</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55480.42469234934</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>46104.68765870777</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>60212.98484765529</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>51407.68744604568</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>55165.18960193404</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>70176.11324328372</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>67279.84453204843</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>65418.92873185271</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>58871.63098931144</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>49576.59235267542</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>28608.64498512408</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>30221.03330162288</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>39958.96152187726</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>56218.47606892</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>110958.0789014279</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>114227.8779710944</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>97932.30695506986</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>101949.8285084604</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>120801.1173720551</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>76215.01799274819</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>122161.0464563577</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>62628.56142679702</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>84972.93904289401</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>83545.98291395989</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>86777.87373623672</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>84854.79851132451</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>69468.56</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>41362.54604555698</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>50762.72378200001</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>60220.1</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>46466.519</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>56764.487</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>48056.15967633893</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>30790.68569767767</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>70889.25733338314</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>72913.62491444954</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>79823.08297607297</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>87467.61277985698</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>64757.12483680325</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>75096.59740076191</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>77394.39151096725</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>80368.24318090208</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>72500.79236117276</v>
       </c>
     </row>
     <row r="4">
@@ -572,37 +1287,232 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>235844.3691802917</v>
+        <v>473551.7256051205</v>
       </c>
       <c r="C4" t="n">
-        <v>256839.1586328733</v>
+        <v>289125.1070240645</v>
       </c>
       <c r="D4" t="n">
-        <v>303522.404038647</v>
+        <v>291264.2097555604</v>
       </c>
       <c r="E4" t="n">
-        <v>302646.485228717</v>
+        <v>265290.3972004985</v>
       </c>
       <c r="F4" t="n">
-        <v>224894.6025179674</v>
+        <v>114112.5414985815</v>
       </c>
       <c r="G4" t="n">
-        <v>225430.4516058913</v>
+        <v>121817.5456611645</v>
       </c>
       <c r="H4" t="n">
-        <v>309924.7517149917</v>
+        <v>108892.3008986797</v>
       </c>
       <c r="I4" t="n">
-        <v>300498.114570479</v>
+        <v>105909.5325135366</v>
       </c>
       <c r="J4" t="n">
-        <v>238538.4729674571</v>
+        <v>111484.5478750699</v>
       </c>
       <c r="K4" t="n">
-        <v>286538.3824025185</v>
+        <v>109472.2600882738</v>
       </c>
       <c r="L4" t="n">
-        <v>256929.2838757988</v>
+        <v>116244.5194148154</v>
+      </c>
+      <c r="M4" t="n">
+        <v>199115.7612302144</v>
+      </c>
+      <c r="N4" t="n">
+        <v>193992.6713055037</v>
+      </c>
+      <c r="O4" t="n">
+        <v>181501.482790138</v>
+      </c>
+      <c r="P4" t="n">
+        <v>242564.5071480609</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>103231.6224955287</v>
+      </c>
+      <c r="R4" t="n">
+        <v>261507.2549050615</v>
+      </c>
+      <c r="S4" t="n">
+        <v>254231.5917755708</v>
+      </c>
+      <c r="T4" t="n">
+        <v>304058.1259623535</v>
+      </c>
+      <c r="U4" t="n">
+        <v>358407.8120985716</v>
+      </c>
+      <c r="V4" t="n">
+        <v>358859.9940626418</v>
+      </c>
+      <c r="W4" t="n">
+        <v>229529.7032113277</v>
+      </c>
+      <c r="X4" t="n">
+        <v>128178.4775853196</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>164250.7310014596</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>84454.53893166859</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>137509.1225537218</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>116059.4480006163</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>136433.9649562255</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>176010.7806602259</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>232357.9356134105</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>186995.9810682866</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>171548.1527937211</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>146742.1151553687</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>151594.3971739073</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>140473.1800386804</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>193938.2604777707</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>154311.1855863388</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>194725.6325791561</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>201981.4260514785</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>199329.6971674449</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>192611.4489821127</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>213835.9100481668</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>165578.8521856312</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>88022.48117669713</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>91797.20238559357</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>116043.5728094426</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>116774.1687569073</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>323028.6516446971</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>341876.5071832517</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>340809.4113786119</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>353206.8537280076</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>302463.3125554243</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>179555.3409466878</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>297502.1754728873</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>147978.1554881051</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>198920.2825271324</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>194530.08111154</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>201584.3046314216</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>196143.1933133978</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>130266.9026416543</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>104347.9899609492</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>98800.74813665493</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>132525.3106954099</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>89022.93597954439</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>115875.8940212374</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>105254.0294787811</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>58464.14349249625</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>183630.6761575444</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>175044.1043340405</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>146071.80647298</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>144246.5465888265</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>100513.7070756429</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>117667.0199494147</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>119128.8110233855</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>125926.097834186</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>116054.7014620051</v>
       </c>
     </row>
     <row r="5">
@@ -612,37 +1522,232 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4421.530275530009</v>
+        <v>3107.197480626479</v>
       </c>
       <c r="C5" t="n">
-        <v>4852.60400171739</v>
+        <v>3907.107878840001</v>
       </c>
       <c r="D5" t="n">
-        <v>4477.84777579591</v>
+        <v>4023.513085708761</v>
       </c>
       <c r="E5" t="n">
-        <v>4653.473496658243</v>
+        <v>5366.744646409529</v>
       </c>
       <c r="F5" t="n">
-        <v>4875.714087512352</v>
+        <v>1359.25498767938</v>
       </c>
       <c r="G5" t="n">
-        <v>4799.42148568716</v>
+        <v>1600.0832314654</v>
       </c>
       <c r="H5" t="n">
-        <v>4852.291779119411</v>
+        <v>1337.88395729494</v>
       </c>
       <c r="I5" t="n">
-        <v>5029.373510375292</v>
+        <v>1405.66328496198</v>
       </c>
       <c r="J5" t="n">
-        <v>5230.576827930286</v>
+        <v>1494.73947601594</v>
       </c>
       <c r="K5" t="n">
-        <v>4583.52085475708</v>
+        <v>1489.13362500364</v>
       </c>
       <c r="L5" t="n">
-        <v>4343.062933130394</v>
+        <v>1509.1074463696</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2126.61689579812</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2162.041501095961</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2000.14977828292</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2276.46511465164</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1226.7300627384</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2385.72528595038</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2474.59840409452</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2104.44524878918</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2561.9020568372</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2501.99007619308</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2340.4220153886</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1409.92334212048</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1738.03316409404</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1091.92548134868</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1851.89239157208</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1246.3122320275</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1891.93994176902</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2011.7999029117</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2415.82215316596</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2052.63830127466</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2222.69414402002</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1973.84876600516</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2091.56599119468</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1514.67558593318</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1985.21760193702</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1593.46558394386</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1648.98713734458</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2244.37839694068</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2254.43683832752</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2066.92516273012</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1760.02604189236</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1519.21504245786</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1076.95905354268</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1127.19433391598</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1213.87284368196</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4165.453600000001</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4252.297358456579</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4702.352021166066</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4035.330859904059</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4348.50614279469</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8630.381030457032</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5798.559819150278</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>9185.706454255054</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4808.572736454925</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5876.131610122532</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5650.116368655028</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6187.381591652433</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>5992.074201495198</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>10880</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>6024.12188755227</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4998.245</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>4802</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>4045</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5112</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>9290.70616454881</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>7300.91952348227</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>7171.871440400177</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>7346.571580202123</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>9005.691306435867</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>9839.459091145916</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>7475.505364055657</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>8156.726880743076</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>8184.260976247137</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>8096.554037333866</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>7164.26178754857</v>
       </c>
     </row>
     <row r="6">
@@ -652,37 +1757,232 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7705.257432622958</v>
+        <v>6025.959491685639</v>
       </c>
       <c r="C6" t="n">
-        <v>8318.969541618622</v>
+        <v>7216.527869111726</v>
       </c>
       <c r="D6" t="n">
-        <v>7911.487875853649</v>
+        <v>7284.263594162116</v>
       </c>
       <c r="E6" t="n">
-        <v>7922.844200489174</v>
+        <v>8825.138567073458</v>
       </c>
       <c r="F6" t="n">
-        <v>8427.832982481199</v>
+        <v>2546.15399105892</v>
       </c>
       <c r="G6" t="n">
-        <v>8199.858264315415</v>
+        <v>3068.051905441875</v>
       </c>
       <c r="H6" t="n">
-        <v>8614.122202285856</v>
+        <v>2598.607777338705</v>
       </c>
       <c r="I6" t="n">
-        <v>8770.851122319431</v>
+        <v>2654.280956773875</v>
       </c>
       <c r="J6" t="n">
-        <v>8605.185852087463</v>
+        <v>2882.75889704484</v>
       </c>
       <c r="K6" t="n">
-        <v>7461.186885505573</v>
+        <v>2804.52838600594</v>
       </c>
       <c r="L6" t="n">
-        <v>7178.439500410393</v>
+        <v>2852.39001631342</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4004.12834834034</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4001.787466183265</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3687.44296444887</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4430.201668836736</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2341.6938567814</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4462.24245831111</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4543.475517760355</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4138.409941566724</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4831.410853993844</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5024.52610154451</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4574.07653503196</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2732.156010943865</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3483.546787763185</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2129.106052835245</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3556.424372644715</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2443.10786849602</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3614.64336907322</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3925.37963255867</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>4638.843987039405</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4095.57302061765</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4192.40398378758</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3835.597061416836</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3948.752549994286</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2982.40827423979</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>3788.826444837115</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3237.347480479586</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3228.055746810895</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4506.990911789576</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>4420.896110090185</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4270.211394749411</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3473.496127631585</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3025.30316487487</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2028.03172740212</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2159.8655237269</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2381.42152558871</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10983.90443333333</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7515.815423920358</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>8120.698926603831</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7250.541152611132</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7650.553751903668</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>16494.61059862406</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10875.52250551388</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>17509.36708087136</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9064.389944347275</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>10315.87191092336</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>10179.2492628067</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>10962.99629254136</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>10720.83894146489</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>16480</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>7864.32899943488</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>8484.61925</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>8615.75</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>7150.75</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>9553.75</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>13023.41370792537</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>9911.003395444628</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>13145.02653676005</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>13315.78471393977</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>15975.1427936593</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>17379.99491511496</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>12806.48669811124</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>13831.87449951545</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>13857.31945828538</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>13731.29031274336</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>12290.72621400194</v>
       </c>
     </row>
     <row r="7">
@@ -692,37 +1992,232 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18033.36240866197</v>
+        <v>13389.96439458389</v>
       </c>
       <c r="C7" t="n">
-        <v>18348.04606612602</v>
+        <v>16442.70140861565</v>
       </c>
       <c r="D7" t="n">
-        <v>15534.60128983051</v>
+        <v>17299.19823943009</v>
       </c>
       <c r="E7" t="n">
-        <v>15518.03783936034</v>
+        <v>17401.07496193696</v>
       </c>
       <c r="F7" t="n">
-        <v>18413.23785794818</v>
+        <v>6433.183825005741</v>
       </c>
       <c r="G7" t="n">
-        <v>17869.46442402063</v>
+        <v>7015.78040724737</v>
       </c>
       <c r="H7" t="n">
-        <v>18842.17553419524</v>
+        <v>5870.717753696181</v>
       </c>
       <c r="I7" t="n">
-        <v>18039.89069266979</v>
+        <v>6147.065370372851</v>
       </c>
       <c r="J7" t="n">
-        <v>18034.2121570603</v>
+        <v>6476.540743917531</v>
       </c>
       <c r="K7" t="n">
-        <v>14332.44107385187</v>
+        <v>6214.62994620039</v>
       </c>
       <c r="L7" t="n">
-        <v>13675.61473580465</v>
+        <v>6456.6186215465</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9074.628919481398</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9238.326657698601</v>
+      </c>
+      <c r="O7" t="n">
+        <v>8522.558075878</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9964.214570911699</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5762.434388313461</v>
+      </c>
+      <c r="R7" t="n">
+        <v>10303.9120137866</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10955.7337303249</v>
+      </c>
+      <c r="T7" t="n">
+        <v>9335.4570101056</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11396.3320206054</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11664.0997843315</v>
+      </c>
+      <c r="W7" t="n">
+        <v>10167.358172081</v>
+      </c>
+      <c r="X7" t="n">
+        <v>6231.530254350941</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7706.623817501511</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4771.44908384727</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8084.3820634192</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6007.061201237471</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8390.5512926499</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>8702.053794065501</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>10443.1617378451</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9494.667979305301</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>9449.625265695999</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>8517.997424867699</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>8953.759173305101</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>6672.179374518571</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>8260.8877062635</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>7221.08691745804</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>7910.137752942701</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>10260.7735740906</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>10057.3663513851</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>9592.8995813376</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7945.3851636027</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6739.87264876871</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4665.676151221471</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4925.5940107616</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5741.803564123111</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>26190.681</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>15609.95655560721</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>16276.91132421246</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>16208.70304617097</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16242.13310949606</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>33956.95077590895</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>21910.83972995546</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>36528.54552456377</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>18743.13274653286</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>20895.1139454473</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>20645.72522610265</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>22114.81404777861</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>21761.65913837581</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>28840</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>13112.9007092155</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>17275.445</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>16104.5</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>14002</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>17878</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>20879.48415664675</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>15366.954286114</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>26072.75352271854</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>27285.0469777728</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>31315.39524706842</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>33227.54828506184</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>24566.68516756937</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>27145.58539021827</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>27687.49253304677</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>27391.84579989535</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>24551.53926768807</v>
       </c>
     </row>
     <row r="8">
@@ -732,37 +2227,232 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55375.63500668944</v>
+        <v>44031.08146310747</v>
       </c>
       <c r="C8" t="n">
-        <v>59500.45153850355</v>
+        <v>55126.11925017054</v>
       </c>
       <c r="D8" t="n">
-        <v>43554.77528704338</v>
+        <v>61120.08269009536</v>
       </c>
       <c r="E8" t="n">
-        <v>44598.01381791079</v>
+        <v>52033.9561581314</v>
       </c>
       <c r="F8" t="n">
-        <v>57644.2969655563</v>
+        <v>20026.11370509145</v>
       </c>
       <c r="G8" t="n">
-        <v>57419.63754724183</v>
+        <v>23027.86612230885</v>
       </c>
       <c r="H8" t="n">
-        <v>54617.01279702976</v>
+        <v>19926.84195719305</v>
       </c>
       <c r="I8" t="n">
-        <v>60695.8389664479</v>
+        <v>19846.2620853024</v>
       </c>
       <c r="J8" t="n">
-        <v>53458.79675728663</v>
+        <v>22248.60827220735</v>
       </c>
       <c r="K8" t="n">
-        <v>41272.63425310593</v>
+        <v>22013.3275329385</v>
       </c>
       <c r="L8" t="n">
-        <v>39662.3256685274</v>
+        <v>21613.9154939796</v>
+      </c>
+      <c r="M8" t="n">
+        <v>33648.93092263835</v>
+      </c>
+      <c r="N8" t="n">
+        <v>35053.19221457405</v>
+      </c>
+      <c r="O8" t="n">
+        <v>31628.8477040085</v>
+      </c>
+      <c r="P8" t="n">
+        <v>37616.85305198095</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>17700.2735157754</v>
+      </c>
+      <c r="R8" t="n">
+        <v>39187.79274214256</v>
+      </c>
+      <c r="S8" t="n">
+        <v>39966.5718136762</v>
+      </c>
+      <c r="T8" t="n">
+        <v>31186.9872460531</v>
+      </c>
+      <c r="U8" t="n">
+        <v>37752.65265688235</v>
+      </c>
+      <c r="V8" t="n">
+        <v>38654.47987959085</v>
+      </c>
+      <c r="W8" t="n">
+        <v>35067.25445316115</v>
+      </c>
+      <c r="X8" t="n">
+        <v>21506.47875430065</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>27969.35883558795</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>18372.4025428702</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>28640.52920546015</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>19058.0786625207</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>27786.2558952638</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>31573.76727096955</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>37809.37527106685</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>34124.092195314</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>32649.78055044255</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>30049.52344707005</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>30619.07768207255</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>22502.82343902835</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>28000.0519628225</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>24930.3631779884</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>24465.6044346989</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>41424.3093516098</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>35633.0089782238</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>34978.26299385385</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>24156.1368434947</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>23240.25844766395</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>15294.15158790585</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>16204.82976138565</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>22008.7041769749</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>58938.8195</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>47926.83632931147</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>49879.80816358644</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>47102.71896187135</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>43830.33723661795</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>97900.5914541083</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>62239.53125919632</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>99410.86126558283</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>51836.51446690785</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>59163.12972596447</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>57568.7952600243</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>62052.53102559906</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>61265.22755491319</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>66740</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>33667.77899637665</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>44654.505</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>42865</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>37320.75</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>48212</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>49682.72769359915</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>31746.90135544375</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>66643.05595088392</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>68071.85131709668</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>80363.27247594061</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>88098.34850070131</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>66910.48043416067</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>78329.48385828419</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>80666.44555846317</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>79466.01860303471</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>68592.90438773579</v>
       </c>
     </row>
     <row r="9">
@@ -772,37 +2462,232 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3441293.778590984</v>
+        <v>8122726.592434363</v>
       </c>
       <c r="C9" t="n">
-        <v>2997519.452074238</v>
+        <v>3086139.294757853</v>
       </c>
       <c r="D9" t="n">
-        <v>3474572.365462308</v>
+        <v>7204266.742329176</v>
       </c>
       <c r="E9" t="n">
-        <v>3766905.59001234</v>
+        <v>2569139.925782104</v>
       </c>
       <c r="F9" t="n">
-        <v>2753403.630072502</v>
+        <v>1698316.65470918</v>
       </c>
       <c r="G9" t="n">
-        <v>2173211.290130805</v>
+        <v>1953657.1430926</v>
       </c>
       <c r="H9" t="n">
-        <v>3039979.376189653</v>
+        <v>2014199.06168294</v>
       </c>
       <c r="I9" t="n">
-        <v>6004868.809911354</v>
+        <v>1790822.73193406</v>
       </c>
       <c r="J9" t="n">
-        <v>2247437.265527637</v>
+        <v>1443755.52817518</v>
       </c>
       <c r="K9" t="n">
-        <v>5375654.536827597</v>
+        <v>1564591.58663698</v>
       </c>
       <c r="L9" t="n">
-        <v>4239740.357313359</v>
+        <v>1970313.74127984</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2470661.90715718</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2527283.75416462</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2105847.42581576</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2421202.90838998</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1466816.39147648</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2861788.170666261</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2785112.37681754</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5038810.982452061</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5636538.305159081</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6049808.34863592</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3456150.8082959</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1599383.84789106</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2408499.85809554</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1153911.62847246</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1847383.16277328</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1924986.18972528</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1963689.22389178</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2583918.8280532</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3856207.218654341</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2799825.38531674</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3081100.34485264</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2326375.29938</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1977546.07586316</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2151719.3254238</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>3293436.0035962</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1824004.88094594</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2693794.69019408</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2287799.90739608</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>3008709.25558984</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2736623.22405714</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3265940.9522993</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2398317.22903388</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1673813.56260536</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1671361.1306579</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1447457.46153008</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2040565.936933333</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2650588.786217585</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2980879.128088631</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>5498558.33502333</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5568349.405127079</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3672230.851263796</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2530817.22048714</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3841111.080042755</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2055972.214523255</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2325577.519082672</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2181179.000166196</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2348400.968177486</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2267621.734259108</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1643440</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1589836.91145789</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1575311</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1276423</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>816687</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1270793</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1392598.80028636</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>746357.568074079</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>3989325.64061538</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>3563066.28214841</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>2186908.808510384</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1465364.870438074</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1073011.442711933</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1145706.187841673</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1027047.573270711</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1107606.637430847</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1026338.674711787</v>
       </c>
     </row>
   </sheetData>
